--- a/research/traditional_assets/database/data/denmark/denmark_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_chemical_specialty.xlsx
@@ -1412,7 +1412,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1549,22 +1549,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08629595181798963</v>
+        <v>0.08614120072399005</v>
       </c>
       <c r="C2">
-        <v>27682.08743756995</v>
+        <v>27502.9296736013</v>
       </c>
       <c r="D2">
-        <v>27402.68743756995</v>
+        <v>27507.8056736013</v>
       </c>
       <c r="E2">
-        <v>-2131.4</v>
+        <v>-1847.124</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>284.276</v>
       </c>
       <c r="G2">
         <v>279.4</v>
@@ -1585,28 +1585,28 @@
         <v>562.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>14.2990828</v>
       </c>
       <c r="N2">
-        <v>562.6</v>
+        <v>548.3009172000001</v>
       </c>
       <c r="O2">
-        <v>123.772</v>
+        <v>120.626201784</v>
       </c>
       <c r="P2">
-        <v>438.828</v>
+        <v>427.674715416</v>
       </c>
       <c r="Q2">
-        <v>591.2280000000001</v>
+        <v>580.074715416</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08629595181798963</v>
+        <v>0.08661501083231318</v>
       </c>
       <c r="T2">
-        <v>0.9352413814778209</v>
+        <v>0.9426099499379491</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>39.34518093705983</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1631,22 +1631,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08614120072399005</v>
+        <v>0.08598644962999047</v>
       </c>
       <c r="C3">
-        <v>27502.9296736013</v>
+        <v>27324.58149406596</v>
       </c>
       <c r="D3">
-        <v>27507.8056736013</v>
+        <v>27613.73349406596</v>
       </c>
       <c r="E3">
-        <v>-1847.124</v>
+        <v>-1562.848</v>
       </c>
       <c r="F3">
-        <v>284.276</v>
+        <v>568.552</v>
       </c>
       <c r="G3">
         <v>279.4</v>
@@ -1667,28 +1667,28 @@
         <v>562.6</v>
       </c>
       <c r="M3">
-        <v>14.2990828</v>
+        <v>28.5981656</v>
       </c>
       <c r="N3">
-        <v>548.3009172000001</v>
+        <v>534.0018344</v>
       </c>
       <c r="O3">
-        <v>120.626201784</v>
+        <v>117.480403568</v>
       </c>
       <c r="P3">
-        <v>427.674715416</v>
+        <v>416.521430832</v>
       </c>
       <c r="Q3">
-        <v>580.074715416</v>
+        <v>568.9214308319999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08661501083231318</v>
+        <v>0.08694058125509233</v>
       </c>
       <c r="T3">
-        <v>0.9426099499379491</v>
+        <v>0.9501288973462433</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>39.34518093705983</v>
+        <v>19.67259046852991</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1713,22 +1713,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08598644962999047</v>
+        <v>0.0858316985359909</v>
       </c>
       <c r="C4">
-        <v>27324.58149406596</v>
+        <v>27147.05228782934</v>
       </c>
       <c r="D4">
-        <v>27613.73349406596</v>
+        <v>27720.48028782934</v>
       </c>
       <c r="E4">
-        <v>-1562.848</v>
+        <v>-1278.572</v>
       </c>
       <c r="F4">
-        <v>568.552</v>
+        <v>852.8280000000001</v>
       </c>
       <c r="G4">
         <v>279.4</v>
@@ -1749,28 +1749,28 @@
         <v>562.6</v>
       </c>
       <c r="M4">
-        <v>28.5981656</v>
+        <v>42.8972484</v>
       </c>
       <c r="N4">
-        <v>534.0018344</v>
+        <v>519.7027516000001</v>
       </c>
       <c r="O4">
-        <v>117.480403568</v>
+        <v>114.334605352</v>
       </c>
       <c r="P4">
-        <v>416.521430832</v>
+        <v>405.368146248</v>
       </c>
       <c r="Q4">
-        <v>568.9214308319999</v>
+        <v>557.768146248</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08694058125509233</v>
+        <v>0.08727286447009372</v>
       </c>
       <c r="T4">
-        <v>0.9501288973462433</v>
+        <v>0.9578028745980075</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>19.67259046852991</v>
+        <v>13.11506031235328</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0858316985359909</v>
+        <v>0.08567694744199132</v>
       </c>
       <c r="C5">
-        <v>27147.05228782934</v>
+        <v>26970.35158949895</v>
       </c>
       <c r="D5">
-        <v>27720.48028782934</v>
+        <v>27828.05558949895</v>
       </c>
       <c r="E5">
-        <v>-1278.572</v>
+        <v>-994.296</v>
       </c>
       <c r="F5">
-        <v>852.8280000000001</v>
+        <v>1137.104</v>
       </c>
       <c r="G5">
         <v>279.4</v>
@@ -1831,28 +1831,28 @@
         <v>562.6</v>
       </c>
       <c r="M5">
-        <v>42.8972484</v>
+        <v>57.1963312</v>
       </c>
       <c r="N5">
-        <v>519.7027516000001</v>
+        <v>505.4036688</v>
       </c>
       <c r="O5">
-        <v>114.334605352</v>
+        <v>111.188807136</v>
       </c>
       <c r="P5">
-        <v>405.368146248</v>
+        <v>394.2148616640001</v>
       </c>
       <c r="Q5">
-        <v>557.768146248</v>
+        <v>546.614861664</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08727286447009372</v>
+        <v>0.08761207025207429</v>
       </c>
       <c r="T5">
-        <v>0.9578028745980075</v>
+        <v>0.9656367263758501</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>13.11506031235328</v>
+        <v>9.836295234264957</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1877,22 +1877,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08567694744199132</v>
+        <v>0.08558069634799174</v>
       </c>
       <c r="C6">
-        <v>26970.35158949895</v>
+        <v>26753.40675864038</v>
       </c>
       <c r="D6">
-        <v>27828.05558949895</v>
+        <v>27895.38675864038</v>
       </c>
       <c r="E6">
-        <v>-994.296</v>
+        <v>-710.02</v>
       </c>
       <c r="F6">
-        <v>1137.104</v>
+        <v>1421.38</v>
       </c>
       <c r="G6">
         <v>279.4</v>
@@ -1913,45 +1913,45 @@
         <v>562.6</v>
       </c>
       <c r="M6">
-        <v>57.1963312</v>
+        <v>73.62748400000001</v>
       </c>
       <c r="N6">
-        <v>505.4036688</v>
+        <v>488.972516</v>
       </c>
       <c r="O6">
-        <v>111.188807136</v>
+        <v>107.57395352</v>
       </c>
       <c r="P6">
-        <v>394.2148616640001</v>
+        <v>381.39856248</v>
       </c>
       <c r="Q6">
-        <v>546.614861664</v>
+        <v>533.79856248</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08761207025207429</v>
+        <v>0.08795841720841237</v>
       </c>
       <c r="T6">
-        <v>0.9656367263758501</v>
+        <v>0.9736355013490157</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>9.836295234264957</v>
+        <v>7.641168344147139</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1959,22 +1959,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08558069634799174</v>
+        <v>0.08551720525399216</v>
       </c>
       <c r="C7">
-        <v>26753.40675864038</v>
+        <v>26513.72374073771</v>
       </c>
       <c r="D7">
-        <v>27895.38675864038</v>
+        <v>27939.97974073771</v>
       </c>
       <c r="E7">
-        <v>-710.02</v>
+        <v>-425.7439999999999</v>
       </c>
       <c r="F7">
-        <v>1421.38</v>
+        <v>1705.656</v>
       </c>
       <c r="G7">
         <v>279.4</v>
@@ -1995,45 +1995,45 @@
         <v>562.6</v>
       </c>
       <c r="M7">
-        <v>73.62748400000001</v>
+        <v>91.25259600000001</v>
       </c>
       <c r="N7">
-        <v>488.972516</v>
+        <v>471.347404</v>
       </c>
       <c r="O7">
-        <v>107.57395352</v>
+        <v>103.69642888</v>
       </c>
       <c r="P7">
-        <v>381.39856248</v>
+        <v>367.65097512</v>
       </c>
       <c r="Q7">
-        <v>533.79856248</v>
+        <v>520.05097512</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08795841720841237</v>
+        <v>0.08831213324892784</v>
       </c>
       <c r="T7">
-        <v>0.9736355013490157</v>
+        <v>0.9818044630237379</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>7.641168344147139</v>
+        <v>6.165304053377286</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2041,22 +2041,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08551720525399216</v>
+        <v>0.0854310941599926</v>
       </c>
       <c r="C8">
-        <v>26513.72374073771</v>
+        <v>26290.1561888085</v>
       </c>
       <c r="D8">
-        <v>27939.97974073771</v>
+        <v>28000.6881888085</v>
       </c>
       <c r="E8">
-        <v>-425.7439999999999</v>
+        <v>-141.4680000000001</v>
       </c>
       <c r="F8">
-        <v>1705.656</v>
+        <v>1989.932</v>
       </c>
       <c r="G8">
         <v>279.4</v>
@@ -2077,45 +2077,45 @@
         <v>562.6</v>
       </c>
       <c r="M8">
-        <v>91.25259600000001</v>
+        <v>108.0533076</v>
       </c>
       <c r="N8">
-        <v>471.347404</v>
+        <v>454.5466924</v>
       </c>
       <c r="O8">
-        <v>103.69642888</v>
+        <v>100.000272328</v>
       </c>
       <c r="P8">
-        <v>367.65097512</v>
+        <v>354.546420072</v>
       </c>
       <c r="Q8">
-        <v>520.05097512</v>
+        <v>506.946420072</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08831213324892784</v>
+        <v>0.08867345608601354</v>
       </c>
       <c r="T8">
-        <v>0.9818044630237379</v>
+        <v>0.9901491012936154</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>6.165304053377286</v>
+        <v>5.206689295275215</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2123,22 +2123,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08543109415999259</v>
+        <v>0.08530754306599303</v>
       </c>
       <c r="C9">
-        <v>26290.15618880851</v>
+        <v>26093.4461417884</v>
       </c>
       <c r="D9">
-        <v>28000.68818880851</v>
+        <v>28088.2541417884</v>
       </c>
       <c r="E9">
-        <v>-141.4679999999998</v>
+        <v>142.808</v>
       </c>
       <c r="F9">
-        <v>1989.932</v>
+        <v>2274.208</v>
       </c>
       <c r="G9">
         <v>279.4</v>
@@ -2159,28 +2159,28 @@
         <v>562.6</v>
       </c>
       <c r="M9">
-        <v>108.0533076</v>
+        <v>123.4894944</v>
       </c>
       <c r="N9">
-        <v>454.5466924</v>
+        <v>439.1105056</v>
       </c>
       <c r="O9">
-        <v>100.000272328</v>
+        <v>96.604311232</v>
       </c>
       <c r="P9">
-        <v>354.546420072</v>
+        <v>342.506194368</v>
       </c>
       <c r="Q9">
-        <v>506.946420072</v>
+        <v>494.906194368</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08867345608601354</v>
+        <v>0.08904263376738372</v>
       </c>
       <c r="T9">
-        <v>0.9901491012936157</v>
+        <v>0.998675144743273</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>5.206689295275214</v>
+        <v>4.555853133365813</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2205,22 +2205,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08530754306599303</v>
+        <v>0.08525419197199346</v>
       </c>
       <c r="C10">
-        <v>26093.4461417884</v>
+        <v>25847.15188750673</v>
       </c>
       <c r="D10">
-        <v>28088.2541417884</v>
+        <v>28126.23588750673</v>
       </c>
       <c r="E10">
-        <v>142.808</v>
+        <v>427.0839999999998</v>
       </c>
       <c r="F10">
-        <v>2274.208</v>
+        <v>2558.484</v>
       </c>
       <c r="G10">
         <v>279.4</v>
@@ -2241,45 +2241,45 @@
         <v>562.6</v>
       </c>
       <c r="M10">
-        <v>123.4894944</v>
+        <v>141.4841652</v>
       </c>
       <c r="N10">
-        <v>439.1105056</v>
+        <v>421.1158348</v>
       </c>
       <c r="O10">
-        <v>96.604311232</v>
+        <v>92.64548365600001</v>
       </c>
       <c r="P10">
-        <v>342.506194368</v>
+        <v>328.470351144</v>
       </c>
       <c r="Q10">
-        <v>494.906194368</v>
+        <v>480.870351144</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08904263376738372</v>
+        <v>0.08941992524394884</v>
       </c>
       <c r="T10">
-        <v>0.998675144743273</v>
+        <v>1.007388573763253</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>4.555853133365813</v>
+        <v>3.97641671917643</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2287,22 +2287,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08525419197199346</v>
+        <v>0.08513844087799387</v>
       </c>
       <c r="C11">
-        <v>25847.15188750673</v>
+        <v>25645.63571482594</v>
       </c>
       <c r="D11">
-        <v>28126.23588750673</v>
+        <v>28208.99571482593</v>
       </c>
       <c r="E11">
-        <v>427.0839999999998</v>
+        <v>711.3599999999997</v>
       </c>
       <c r="F11">
-        <v>2558.484</v>
+        <v>2842.76</v>
       </c>
       <c r="G11">
         <v>279.4</v>
@@ -2323,28 +2323,28 @@
         <v>562.6</v>
       </c>
       <c r="M11">
-        <v>141.4841652</v>
+        <v>157.204628</v>
       </c>
       <c r="N11">
-        <v>421.1158348</v>
+        <v>405.3953720000001</v>
       </c>
       <c r="O11">
-        <v>92.64548365600001</v>
+        <v>89.18698184000002</v>
       </c>
       <c r="P11">
-        <v>328.470351144</v>
+        <v>316.20839016</v>
       </c>
       <c r="Q11">
-        <v>480.870351144</v>
+        <v>468.60839016</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08941992524394884</v>
+        <v>0.08980560097554874</v>
       </c>
       <c r="T11">
-        <v>1.007388573763253</v>
+        <v>1.016295634539232</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2361,7 +2361,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>3.97641671917643</v>
+        <v>3.578775047258787</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2369,22 +2369,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08513844087799387</v>
+        <v>0.08502268978399428</v>
       </c>
       <c r="C12">
-        <v>25645.63571482593</v>
+        <v>25444.60801147777</v>
       </c>
       <c r="D12">
-        <v>28208.99571482593</v>
+        <v>28292.24401147776</v>
       </c>
       <c r="E12">
-        <v>711.3600000000001</v>
+        <v>995.636</v>
       </c>
       <c r="F12">
-        <v>2842.76</v>
+        <v>3127.036</v>
       </c>
       <c r="G12">
         <v>279.4</v>
@@ -2405,28 +2405,28 @@
         <v>562.6</v>
       </c>
       <c r="M12">
-        <v>157.204628</v>
+        <v>172.9250908</v>
       </c>
       <c r="N12">
-        <v>405.395372</v>
+        <v>389.6749092</v>
       </c>
       <c r="O12">
-        <v>89.18698184</v>
+        <v>85.72848002400001</v>
       </c>
       <c r="P12">
-        <v>316.20839016</v>
+        <v>303.946429176</v>
       </c>
       <c r="Q12">
-        <v>468.60839016</v>
+        <v>456.346429176</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08980560097554874</v>
+        <v>0.09019994357752167</v>
       </c>
       <c r="T12">
-        <v>1.016295634539232</v>
+        <v>1.025402853984335</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>3.578775047258786</v>
+        <v>3.253431861144351</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2451,22 +2451,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08502268978399428</v>
+        <v>0.0851409386899947</v>
       </c>
       <c r="C13">
-        <v>25444.60801147777</v>
+        <v>25075.29268567477</v>
       </c>
       <c r="D13">
-        <v>28292.24401147776</v>
+        <v>28207.20468567477</v>
       </c>
       <c r="E13">
-        <v>995.636</v>
+        <v>1279.912</v>
       </c>
       <c r="F13">
-        <v>3127.036</v>
+        <v>3411.312</v>
       </c>
       <c r="G13">
         <v>279.4</v>
@@ -2487,45 +2487,45 @@
         <v>562.6</v>
       </c>
       <c r="M13">
-        <v>172.9250908</v>
+        <v>197.1738336</v>
       </c>
       <c r="N13">
-        <v>389.6749092</v>
+        <v>365.4261664</v>
       </c>
       <c r="O13">
-        <v>85.72848002400001</v>
+        <v>80.393756608</v>
       </c>
       <c r="P13">
-        <v>303.946429176</v>
+        <v>285.032409792</v>
       </c>
       <c r="Q13">
-        <v>456.346429176</v>
+        <v>437.432409792</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09019994357752167</v>
+        <v>0.09060324851135762</v>
       </c>
       <c r="T13">
-        <v>1.025402853984335</v>
+        <v>1.034717055689553</v>
       </c>
       <c r="U13">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.253431861144351</v>
+        <v>2.853319782488623</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2533,22 +2533,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0851409386899947</v>
+        <v>0.08504468759599512</v>
       </c>
       <c r="C14">
-        <v>25075.29268567477</v>
+        <v>24860.19736912461</v>
       </c>
       <c r="D14">
-        <v>28207.20468567477</v>
+        <v>28276.38536912461</v>
       </c>
       <c r="E14">
-        <v>1279.912</v>
+        <v>1564.188</v>
       </c>
       <c r="F14">
-        <v>3411.312</v>
+        <v>3695.588</v>
       </c>
       <c r="G14">
         <v>279.4</v>
@@ -2569,28 +2569,28 @@
         <v>562.6</v>
       </c>
       <c r="M14">
-        <v>197.1738336</v>
+        <v>213.6049864</v>
       </c>
       <c r="N14">
-        <v>365.4261664</v>
+        <v>348.9950136</v>
       </c>
       <c r="O14">
-        <v>80.393756608</v>
+        <v>76.778902992</v>
       </c>
       <c r="P14">
-        <v>285.032409792</v>
+        <v>272.216110608</v>
       </c>
       <c r="Q14">
-        <v>437.432409792</v>
+        <v>424.616110608</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09060324851135762</v>
+        <v>0.0910158248229829</v>
       </c>
       <c r="T14">
-        <v>1.034717055689553</v>
+        <v>1.044245376974201</v>
       </c>
       <c r="U14">
         <v>0.0578</v>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>2.853319782488623</v>
+        <v>2.633833645374113</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2615,22 +2615,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08504468759599512</v>
+        <v>0.08533063650199556</v>
       </c>
       <c r="C15">
-        <v>24860.19736912461</v>
+        <v>24371.38124082336</v>
       </c>
       <c r="D15">
-        <v>28276.38536912461</v>
+        <v>28071.84524082336</v>
       </c>
       <c r="E15">
-        <v>1564.188</v>
+        <v>1848.464</v>
       </c>
       <c r="F15">
-        <v>3695.588</v>
+        <v>3979.864</v>
       </c>
       <c r="G15">
         <v>279.4</v>
@@ -2651,45 +2651,45 @@
         <v>562.6</v>
       </c>
       <c r="M15">
-        <v>213.6049864</v>
+        <v>243.9656632</v>
       </c>
       <c r="N15">
-        <v>348.9950136</v>
+        <v>318.6343368</v>
       </c>
       <c r="O15">
-        <v>76.778902992</v>
+        <v>70.09955409600001</v>
       </c>
       <c r="P15">
-        <v>272.216110608</v>
+        <v>248.534782704</v>
       </c>
       <c r="Q15">
-        <v>424.616110608</v>
+        <v>400.934782704</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0910158248229829</v>
+        <v>0.09143799593255297</v>
       </c>
       <c r="T15">
-        <v>1.044245376974201</v>
+        <v>1.053995287125935</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.633833645374113</v>
+        <v>2.306062224579479</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2697,22 +2697,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08533063650199556</v>
+        <v>0.08558928540799599</v>
       </c>
       <c r="C16">
-        <v>24371.38124082336</v>
+        <v>23904.62515889927</v>
       </c>
       <c r="D16">
-        <v>28071.84524082336</v>
+        <v>27889.36515889927</v>
       </c>
       <c r="E16">
-        <v>1848.464</v>
+        <v>2132.740000000001</v>
       </c>
       <c r="F16">
-        <v>3979.864</v>
+        <v>4264.140000000001</v>
       </c>
       <c r="G16">
         <v>279.4</v>
@@ -2733,45 +2733,45 @@
         <v>562.6</v>
       </c>
       <c r="M16">
-        <v>243.9656632</v>
+        <v>273.3313740000001</v>
       </c>
       <c r="N16">
-        <v>318.6343368</v>
+        <v>289.2686259999999</v>
       </c>
       <c r="O16">
-        <v>70.09955409600001</v>
+        <v>63.63909771999998</v>
       </c>
       <c r="P16">
-        <v>248.534782704</v>
+        <v>225.6295282799999</v>
       </c>
       <c r="Q16">
-        <v>400.934782704</v>
+        <v>378.0295282799999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09143799593255297</v>
+        <v>0.09187010047999528</v>
       </c>
       <c r="T16">
-        <v>1.053995287125935</v>
+        <v>1.063974606928297</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>2.306062224579479</v>
+        <v>2.058307437476972</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2779,22 +2779,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08558928540799599</v>
+        <v>0.08700233431399639</v>
       </c>
       <c r="C17">
-        <v>23904.62515889927</v>
+        <v>22663.8733285131</v>
       </c>
       <c r="D17">
-        <v>27889.36515889927</v>
+        <v>26932.8893285131</v>
       </c>
       <c r="E17">
-        <v>2132.74</v>
+        <v>2417.016</v>
       </c>
       <c r="F17">
-        <v>4264.14</v>
+        <v>4548.416</v>
       </c>
       <c r="G17">
         <v>279.4</v>
@@ -2815,45 +2815,45 @@
         <v>562.6</v>
       </c>
       <c r="M17">
-        <v>273.331374</v>
+        <v>344.7699328</v>
       </c>
       <c r="N17">
-        <v>289.268626</v>
+        <v>217.8300672</v>
       </c>
       <c r="O17">
-        <v>63.63909772</v>
+        <v>47.922614784</v>
       </c>
       <c r="P17">
-        <v>225.62952828</v>
+        <v>169.907452416</v>
       </c>
       <c r="Q17">
-        <v>378.02952828</v>
+        <v>322.3074524159999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09187010047999528</v>
+        <v>0.09231249323094809</v>
       </c>
       <c r="T17">
-        <v>1.063974606928297</v>
+        <v>1.074191529583097</v>
       </c>
       <c r="U17">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04999800000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.058307437476972</v>
+        <v>1.63181283075042</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08700233431399639</v>
+        <v>0.08704648321999683</v>
       </c>
       <c r="C18">
-        <v>22663.8733285131</v>
+        <v>22350.76923199532</v>
       </c>
       <c r="D18">
-        <v>26932.8893285131</v>
+        <v>26904.06123199532</v>
       </c>
       <c r="E18">
-        <v>2417.016</v>
+        <v>2701.292000000001</v>
       </c>
       <c r="F18">
-        <v>4548.416</v>
+        <v>4832.692000000001</v>
       </c>
       <c r="G18">
         <v>279.4</v>
@@ -2897,28 +2897,28 @@
         <v>562.6</v>
       </c>
       <c r="M18">
-        <v>344.7699328</v>
+        <v>366.3180536000001</v>
       </c>
       <c r="N18">
-        <v>217.8300672</v>
+        <v>196.2819463999999</v>
       </c>
       <c r="O18">
-        <v>47.922614784</v>
+        <v>43.18202820799998</v>
       </c>
       <c r="P18">
-        <v>169.907452416</v>
+        <v>153.0999181919999</v>
       </c>
       <c r="Q18">
-        <v>322.3074524159999</v>
+        <v>305.4999181919999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09231249323094809</v>
+        <v>0.09276554604818896</v>
       </c>
       <c r="T18">
-        <v>1.074191529583097</v>
+        <v>1.084654643145242</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>1.63181283075042</v>
+        <v>1.535823840706277</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2943,22 +2943,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08704648321999683</v>
+        <v>0.09355936272763046</v>
       </c>
       <c r="C19">
-        <v>22350.76923199532</v>
+        <v>18397.62289825006</v>
       </c>
       <c r="D19">
-        <v>26904.06123199532</v>
+        <v>23235.19089825006</v>
       </c>
       <c r="E19">
-        <v>2701.292000000001</v>
+        <v>2985.568000000001</v>
       </c>
       <c r="F19">
-        <v>4832.692000000001</v>
+        <v>5116.968000000001</v>
       </c>
       <c r="G19">
         <v>279.4</v>
@@ -2979,45 +2979,45 @@
         <v>562.6</v>
       </c>
       <c r="M19">
-        <v>366.3180536000001</v>
+        <v>606.8724048000001</v>
       </c>
       <c r="N19">
-        <v>196.2819463999999</v>
+        <v>-44.27240480000012</v>
       </c>
       <c r="O19">
-        <v>43.18202820799998</v>
+        <v>-9.739929056000026</v>
       </c>
       <c r="P19">
-        <v>153.0999181919999</v>
+        <v>-34.5324757440001</v>
       </c>
       <c r="Q19">
-        <v>305.4999181919999</v>
+        <v>117.8675242559999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09276554604818896</v>
+        <v>0.09337231762210427</v>
       </c>
       <c r="T19">
-        <v>1.084654643145242</v>
+        <v>1.098667843466612</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V19">
-        <v>0.22</v>
+        <v>0.2039506146943526</v>
       </c>
       <c r="W19">
-        <v>0.05912400000000001</v>
+        <v>0.0944114570972498</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y19">
-        <v>1.535823840706277</v>
+        <v>0.9270482486106936</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09355936272763048</v>
+        <v>0.09428736272763047</v>
       </c>
       <c r="C20">
-        <v>18397.62289825005</v>
+        <v>17764.48859739867</v>
       </c>
       <c r="D20">
-        <v>23235.19089825005</v>
+        <v>22886.33259739867</v>
       </c>
       <c r="E20">
-        <v>2985.568</v>
+        <v>3269.844000000001</v>
       </c>
       <c r="F20">
-        <v>5116.968</v>
+        <v>5401.244000000001</v>
       </c>
       <c r="G20">
         <v>279.4</v>
@@ -3061,37 +3061,37 @@
         <v>562.6</v>
       </c>
       <c r="M20">
-        <v>606.8724048</v>
+        <v>640.5875384000001</v>
       </c>
       <c r="N20">
-        <v>-44.2724048</v>
+        <v>-77.98753840000006</v>
       </c>
       <c r="O20">
-        <v>-9.739929056000001</v>
+        <v>-17.15725844800001</v>
       </c>
       <c r="P20">
-        <v>-34.532475744</v>
+        <v>-60.83027995200005</v>
       </c>
       <c r="Q20">
-        <v>117.867524256</v>
+        <v>91.56972004799994</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09337231762210427</v>
+        <v>0.09395963018534012</v>
       </c>
       <c r="T20">
-        <v>1.098667843466612</v>
+        <v>1.112231644003236</v>
       </c>
       <c r="U20">
         <v>0.1186</v>
       </c>
       <c r="V20">
-        <v>0.2039506146943526</v>
+        <v>0.1932163718157025</v>
       </c>
       <c r="W20">
-        <v>0.0944114570972498</v>
+        <v>0.09568453830265769</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.9270482486106938</v>
+        <v>0.8782562355259204</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3107,22 +3107,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09428736272763047</v>
+        <v>0.09501536272763048</v>
       </c>
       <c r="C21">
-        <v>17764.48859739867</v>
+        <v>17141.67501060664</v>
       </c>
       <c r="D21">
-        <v>22886.33259739867</v>
+        <v>22547.79501060664</v>
       </c>
       <c r="E21">
-        <v>3269.844000000001</v>
+        <v>3554.12</v>
       </c>
       <c r="F21">
-        <v>5401.244000000001</v>
+        <v>5685.52</v>
       </c>
       <c r="G21">
         <v>279.4</v>
@@ -3143,37 +3143,37 @@
         <v>562.6</v>
       </c>
       <c r="M21">
-        <v>640.5875384000001</v>
+        <v>674.3026720000001</v>
       </c>
       <c r="N21">
-        <v>-77.98753840000006</v>
+        <v>-111.7026720000001</v>
       </c>
       <c r="O21">
-        <v>-17.15725844800001</v>
+        <v>-24.57458784000003</v>
       </c>
       <c r="P21">
-        <v>-60.83027995200005</v>
+        <v>-87.1280841600001</v>
       </c>
       <c r="Q21">
-        <v>91.56972004799994</v>
+        <v>65.27191583999988</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09395963018534012</v>
+        <v>0.09456162556265688</v>
       </c>
       <c r="T21">
-        <v>1.112231644003236</v>
+        <v>1.126134539553277</v>
       </c>
       <c r="U21">
         <v>0.1186</v>
       </c>
       <c r="V21">
-        <v>0.1932163718157025</v>
+        <v>0.1835555532249173</v>
       </c>
       <c r="W21">
-        <v>0.09568453830265769</v>
+        <v>0.09683031138752481</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.8782562355259204</v>
+        <v>0.8343434237496243</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3189,22 +3189,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09501536272763048</v>
+        <v>0.1136139421222442</v>
       </c>
       <c r="C22">
-        <v>17141.67501060664</v>
+        <v>10673.46481426848</v>
       </c>
       <c r="D22">
-        <v>22547.79501060664</v>
+        <v>16363.86081426848</v>
       </c>
       <c r="E22">
-        <v>3554.12</v>
+        <v>3838.396000000001</v>
       </c>
       <c r="F22">
-        <v>5685.52</v>
+        <v>5969.796000000001</v>
       </c>
       <c r="G22">
         <v>279.4</v>
@@ -3225,45 +3225,45 @@
         <v>562.6</v>
       </c>
       <c r="M22">
-        <v>674.3026720000001</v>
+        <v>1198.7350368</v>
       </c>
       <c r="N22">
-        <v>-111.7026720000001</v>
+        <v>-636.1350368000002</v>
       </c>
       <c r="O22">
-        <v>-24.57458784000003</v>
+        <v>-139.9497080960001</v>
       </c>
       <c r="P22">
-        <v>-87.1280841600001</v>
+        <v>-496.1853287040001</v>
       </c>
       <c r="Q22">
-        <v>65.27191583999988</v>
+        <v>-343.7853287040002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09456162556265688</v>
+        <v>0.09594921499334078</v>
       </c>
       <c r="T22">
-        <v>1.126134539553277</v>
+        <v>1.15818048483466</v>
       </c>
       <c r="U22">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.1835555532249173</v>
+        <v>0.1032521751682565</v>
       </c>
       <c r="W22">
-        <v>0.09683031138752481</v>
+        <v>0.1800669632262141</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y22">
-        <v>0.8343434237496243</v>
+        <v>0.4693280689466204</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3271,22 +3271,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1136139421222442</v>
+        <v>0.1151639421222442</v>
       </c>
       <c r="C23">
-        <v>10673.46481426849</v>
+        <v>10023.52354949135</v>
       </c>
       <c r="D23">
-        <v>16363.86081426849</v>
+        <v>15998.19554949135</v>
       </c>
       <c r="E23">
-        <v>3838.396</v>
+        <v>4122.672</v>
       </c>
       <c r="F23">
-        <v>5969.796</v>
+        <v>6254.072</v>
       </c>
       <c r="G23">
         <v>279.4</v>
@@ -3307,37 +3307,37 @@
         <v>562.6</v>
       </c>
       <c r="M23">
-        <v>1198.7350368</v>
+        <v>1255.8176576</v>
       </c>
       <c r="N23">
-        <v>-636.1350368</v>
+        <v>-693.2176576000001</v>
       </c>
       <c r="O23">
-        <v>-139.949708096</v>
+        <v>-152.507884672</v>
       </c>
       <c r="P23">
-        <v>-496.185328704</v>
+        <v>-540.709772928</v>
       </c>
       <c r="Q23">
-        <v>-343.785328704</v>
+        <v>-388.309772928</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09594921499334078</v>
+        <v>0.09659215364710154</v>
       </c>
       <c r="T23">
-        <v>1.15818048483466</v>
+        <v>1.17302895258895</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.1032521751682565</v>
+        <v>0.09855889447879029</v>
       </c>
       <c r="W23">
-        <v>0.1800669632262141</v>
+        <v>0.1810093739886589</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.4693280689466205</v>
+        <v>0.4479949749035922</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3353,22 +3353,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1151639421222442</v>
+        <v>0.1167139421222441</v>
       </c>
       <c r="C24">
-        <v>10023.52354949135</v>
+        <v>9389.567326398337</v>
       </c>
       <c r="D24">
-        <v>15998.19554949135</v>
+        <v>15648.51532639834</v>
       </c>
       <c r="E24">
-        <v>4122.672</v>
+        <v>4406.948</v>
       </c>
       <c r="F24">
-        <v>6254.072</v>
+        <v>6538.348000000001</v>
       </c>
       <c r="G24">
         <v>279.4</v>
@@ -3389,37 +3389,37 @@
         <v>562.6</v>
       </c>
       <c r="M24">
-        <v>1255.8176576</v>
+        <v>1312.9002784</v>
       </c>
       <c r="N24">
-        <v>-693.2176576000001</v>
+        <v>-750.3002784000001</v>
       </c>
       <c r="O24">
-        <v>-152.507884672</v>
+        <v>-165.066061248</v>
       </c>
       <c r="P24">
-        <v>-540.709772928</v>
+        <v>-585.2342171520002</v>
       </c>
       <c r="Q24">
-        <v>-388.309772928</v>
+        <v>-432.8342171520002</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09659215364710154</v>
+        <v>0.0972517920061548</v>
       </c>
       <c r="T24">
-        <v>1.17302895258895</v>
+        <v>1.188263094830365</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.09855889447879029</v>
+        <v>0.09427372515362549</v>
       </c>
       <c r="W24">
-        <v>0.1810093739886589</v>
+        <v>0.181869835989152</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.4479949749035922</v>
+        <v>0.4285169325164795</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3435,22 +3435,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1167139421222441</v>
+        <v>0.1182639421222442</v>
       </c>
       <c r="C25">
-        <v>9389.567326398337</v>
+        <v>8770.570387327702</v>
       </c>
       <c r="D25">
-        <v>15648.51532639834</v>
+        <v>15313.7943873277</v>
       </c>
       <c r="E25">
-        <v>4406.948</v>
+        <v>4691.224</v>
       </c>
       <c r="F25">
-        <v>6538.348000000001</v>
+        <v>6822.624000000001</v>
       </c>
       <c r="G25">
         <v>279.4</v>
@@ -3471,37 +3471,37 @@
         <v>562.6</v>
       </c>
       <c r="M25">
-        <v>1312.9002784</v>
+        <v>1369.9828992</v>
       </c>
       <c r="N25">
-        <v>-750.3002784000001</v>
+        <v>-807.3828992000002</v>
       </c>
       <c r="O25">
-        <v>-165.066061248</v>
+        <v>-177.6242378240001</v>
       </c>
       <c r="P25">
-        <v>-585.2342171520002</v>
+        <v>-629.7586613760002</v>
       </c>
       <c r="Q25">
-        <v>-432.8342171520002</v>
+        <v>-477.3586613760002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0972517920061548</v>
+        <v>0.09792878926939369</v>
       </c>
       <c r="T25">
-        <v>1.188263094830365</v>
+        <v>1.203898135551817</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.09427372515362549</v>
+        <v>0.09034565327222442</v>
       </c>
       <c r="W25">
-        <v>0.181869835989152</v>
+        <v>0.1826585928229373</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.4285169325164795</v>
+        <v>0.4106620603282929</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3517,22 +3517,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1182639421222442</v>
+        <v>0.1198139421222442</v>
       </c>
       <c r="C26">
-        <v>8770.570387327702</v>
+        <v>8165.592900286868</v>
       </c>
       <c r="D26">
-        <v>15313.7943873277</v>
+        <v>14993.09290028687</v>
       </c>
       <c r="E26">
-        <v>4691.224</v>
+        <v>4975.5</v>
       </c>
       <c r="F26">
-        <v>6822.624000000001</v>
+        <v>7106.900000000001</v>
       </c>
       <c r="G26">
         <v>279.4</v>
@@ -3553,37 +3553,37 @@
         <v>562.6</v>
       </c>
       <c r="M26">
-        <v>1369.9828992</v>
+        <v>1427.06552</v>
       </c>
       <c r="N26">
-        <v>-807.3828992000002</v>
+        <v>-864.4655200000001</v>
       </c>
       <c r="O26">
-        <v>-177.6242378240001</v>
+        <v>-190.1824144</v>
       </c>
       <c r="P26">
-        <v>-629.7586613760002</v>
+        <v>-674.2831056</v>
       </c>
       <c r="Q26">
-        <v>-477.3586613760002</v>
+        <v>-521.8831056</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09792878926939369</v>
+        <v>0.0986238397929856</v>
       </c>
       <c r="T26">
-        <v>1.203898135551817</v>
+        <v>1.219950110692508</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.09034565327222442</v>
+        <v>0.08673182714133545</v>
       </c>
       <c r="W26">
-        <v>0.1826585928229373</v>
+        <v>0.1833842491100199</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4106620603282929</v>
+        <v>0.3942355779151612</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3599,22 +3599,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1198139421222442</v>
+        <v>0.1213639421222442</v>
       </c>
       <c r="C27">
-        <v>8165.592900286868</v>
+        <v>7573.772146231436</v>
       </c>
       <c r="D27">
-        <v>14993.09290028687</v>
+        <v>14685.54814623144</v>
       </c>
       <c r="E27">
-        <v>4975.5</v>
+        <v>5259.776</v>
       </c>
       <c r="F27">
-        <v>7106.900000000001</v>
+        <v>7391.176</v>
       </c>
       <c r="G27">
         <v>279.4</v>
@@ -3635,37 +3635,37 @@
         <v>562.6</v>
       </c>
       <c r="M27">
-        <v>1427.06552</v>
+        <v>1484.1481408</v>
       </c>
       <c r="N27">
-        <v>-864.4655200000001</v>
+        <v>-921.5481408000002</v>
       </c>
       <c r="O27">
-        <v>-190.1824144</v>
+        <v>-202.740590976</v>
       </c>
       <c r="P27">
-        <v>-674.2831056</v>
+        <v>-718.8075498240001</v>
       </c>
       <c r="Q27">
-        <v>-521.8831056</v>
+        <v>-566.4075498240002</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0986238397929856</v>
+        <v>0.09933767546586381</v>
       </c>
       <c r="T27">
-        <v>1.219950110692508</v>
+        <v>1.236435922999164</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.08673182714133545</v>
+        <v>0.08339598763589948</v>
       </c>
       <c r="W27">
-        <v>0.1833842491100199</v>
+        <v>0.1840540856827114</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3942355779151612</v>
+        <v>0.3790726710722703</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3681,22 +3681,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1213639421222442</v>
+        <v>0.1229139421222442</v>
       </c>
       <c r="C28">
-        <v>7573.772146231436</v>
+        <v>6994.314769165081</v>
       </c>
       <c r="D28">
-        <v>14685.54814623144</v>
+        <v>14390.36676916508</v>
       </c>
       <c r="E28">
-        <v>5259.776</v>
+        <v>5544.052000000001</v>
       </c>
       <c r="F28">
-        <v>7391.176</v>
+        <v>7675.452000000001</v>
       </c>
       <c r="G28">
         <v>279.4</v>
@@ -3717,37 +3717,37 @@
         <v>562.6</v>
       </c>
       <c r="M28">
-        <v>1484.1481408</v>
+        <v>1541.2307616</v>
       </c>
       <c r="N28">
-        <v>-921.5481408000002</v>
+        <v>-978.6307616000003</v>
       </c>
       <c r="O28">
-        <v>-202.740590976</v>
+        <v>-215.298767552</v>
       </c>
       <c r="P28">
-        <v>-718.8075498240001</v>
+        <v>-763.3319940480002</v>
       </c>
       <c r="Q28">
-        <v>-566.4075498240002</v>
+        <v>-610.9319940480002</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09933767546586381</v>
+        <v>0.1000710682804647</v>
       </c>
       <c r="T28">
-        <v>1.236435922999164</v>
+        <v>1.253373401396413</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.08339598763589948</v>
+        <v>0.08030724735308838</v>
       </c>
       <c r="W28">
-        <v>0.1840540856827114</v>
+        <v>0.1846743047314999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3790726710722703</v>
+        <v>0.3650329425140381</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3763,22 +3763,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1229139421222442</v>
+        <v>0.1244639421222442</v>
       </c>
       <c r="C29">
-        <v>6994.314769165081</v>
+        <v>6426.489942467028</v>
       </c>
       <c r="D29">
-        <v>14390.36676916508</v>
+        <v>14106.81794246703</v>
       </c>
       <c r="E29">
-        <v>5544.052000000001</v>
+        <v>5828.328000000001</v>
       </c>
       <c r="F29">
-        <v>7675.452000000001</v>
+        <v>7959.728000000001</v>
       </c>
       <c r="G29">
         <v>279.4</v>
@@ -3799,37 +3799,37 @@
         <v>562.6</v>
       </c>
       <c r="M29">
-        <v>1541.2307616</v>
+        <v>1598.3133824</v>
       </c>
       <c r="N29">
-        <v>-978.6307616000003</v>
+        <v>-1035.7133824</v>
       </c>
       <c r="O29">
-        <v>-215.298767552</v>
+        <v>-227.856944128</v>
       </c>
       <c r="P29">
-        <v>-763.3319940480002</v>
+        <v>-807.8564382720002</v>
       </c>
       <c r="Q29">
-        <v>-610.9319940480002</v>
+        <v>-655.4564382720002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1000710682804647</v>
+        <v>0.1008248331176933</v>
       </c>
       <c r="T29">
-        <v>1.253373401396413</v>
+        <v>1.270781365304696</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.08030724735308838</v>
+        <v>0.07743913137619238</v>
       </c>
       <c r="W29">
-        <v>0.1846743047314999</v>
+        <v>0.1852502224196606</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3650329425140381</v>
+        <v>0.3519960517099653</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3845,22 +3845,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1244639421222442</v>
+        <v>0.1260139421222442</v>
       </c>
       <c r="C30">
-        <v>6426.489942467028</v>
+        <v>5869.623327515064</v>
       </c>
       <c r="D30">
-        <v>14106.81794246703</v>
+        <v>13834.22732751507</v>
       </c>
       <c r="E30">
-        <v>5828.328000000001</v>
+        <v>6112.604000000001</v>
       </c>
       <c r="F30">
-        <v>7959.728000000001</v>
+        <v>8244.004000000001</v>
       </c>
       <c r="G30">
         <v>279.4</v>
@@ -3881,37 +3881,37 @@
         <v>562.6</v>
       </c>
       <c r="M30">
-        <v>1598.3133824</v>
+        <v>1655.3960032</v>
       </c>
       <c r="N30">
-        <v>-1035.7133824</v>
+        <v>-1092.7960032</v>
       </c>
       <c r="O30">
-        <v>-227.856944128</v>
+        <v>-240.415120704</v>
       </c>
       <c r="P30">
-        <v>-807.8564382720002</v>
+        <v>-852.380882496</v>
       </c>
       <c r="Q30">
-        <v>-655.4564382720002</v>
+        <v>-699.980882496</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1008248331176933</v>
+        <v>0.1015998307672383</v>
       </c>
       <c r="T30">
-        <v>1.270781365304696</v>
+        <v>1.288679694393495</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.07743913137619238</v>
+        <v>0.07476881650115125</v>
       </c>
       <c r="W30">
-        <v>0.1852502224196606</v>
+        <v>0.1857864216465688</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3519960517099653</v>
+        <v>0.3398582568234149</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1260139421222441</v>
+        <v>0.1275639421222442</v>
       </c>
       <c r="C31">
-        <v>5869.62332751507</v>
+        <v>5323.09171946734</v>
       </c>
       <c r="D31">
-        <v>13834.22732751507</v>
+        <v>13571.97171946734</v>
       </c>
       <c r="E31">
-        <v>6112.604000000001</v>
+        <v>6396.880000000001</v>
       </c>
       <c r="F31">
-        <v>8244.004000000001</v>
+        <v>8528.280000000001</v>
       </c>
       <c r="G31">
         <v>279.4</v>
@@ -3963,37 +3963,37 @@
         <v>562.6</v>
       </c>
       <c r="M31">
-        <v>1655.3960032</v>
+        <v>1712.478624</v>
       </c>
       <c r="N31">
-        <v>-1092.7960032</v>
+        <v>-1149.878624</v>
       </c>
       <c r="O31">
-        <v>-240.415120704</v>
+        <v>-252.97329728</v>
       </c>
       <c r="P31">
-        <v>-852.380882496</v>
+        <v>-896.9053267199999</v>
       </c>
       <c r="Q31">
-        <v>-699.980882496</v>
+        <v>-744.50532672</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1015998307672383</v>
+        <v>0.1023969712067703</v>
       </c>
       <c r="T31">
-        <v>1.288679694393495</v>
+        <v>1.307089404313402</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.07476881650115125</v>
+        <v>0.07227652261777955</v>
       </c>
       <c r="W31">
-        <v>0.1857864216465688</v>
+        <v>0.1862868742583499</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3398582568234149</v>
+        <v>0.3285296482626344</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4009,22 +4009,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1275639421222442</v>
+        <v>0.1291139421222441</v>
       </c>
       <c r="C32">
-        <v>5323.09171946734</v>
+        <v>4786.318290713965</v>
       </c>
       <c r="D32">
-        <v>13571.97171946734</v>
+        <v>13319.47429071397</v>
       </c>
       <c r="E32">
-        <v>6396.880000000001</v>
+        <v>6681.156000000001</v>
       </c>
       <c r="F32">
-        <v>8528.280000000001</v>
+        <v>8812.556</v>
       </c>
       <c r="G32">
         <v>279.4</v>
@@ -4045,37 +4045,37 @@
         <v>562.6</v>
       </c>
       <c r="M32">
-        <v>1712.478624</v>
+        <v>1769.5612448</v>
       </c>
       <c r="N32">
-        <v>-1149.878624</v>
+        <v>-1206.9612448</v>
       </c>
       <c r="O32">
-        <v>-252.97329728</v>
+        <v>-265.531473856</v>
       </c>
       <c r="P32">
-        <v>-896.9053267199999</v>
+        <v>-941.4297709440002</v>
       </c>
       <c r="Q32">
-        <v>-744.50532672</v>
+        <v>-789.0297709440002</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1023969712067703</v>
+        <v>0.1032172171662887</v>
       </c>
       <c r="T32">
-        <v>1.307089404313402</v>
+        <v>1.326032729013596</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.07227652261777955</v>
+        <v>0.06994502188817375</v>
       </c>
       <c r="W32">
-        <v>0.1862868742583499</v>
+        <v>0.1867550396048547</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3285296482626344</v>
+        <v>0.317931917673517</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4091,22 +4091,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1291139421222441</v>
+        <v>0.1306639421222442</v>
       </c>
       <c r="C33">
-        <v>4786.318290713965</v>
+        <v>4258.768355585333</v>
       </c>
       <c r="D33">
-        <v>13319.47429071397</v>
+        <v>13076.20035558533</v>
       </c>
       <c r="E33">
-        <v>6681.156000000001</v>
+        <v>6965.432000000001</v>
       </c>
       <c r="F33">
-        <v>8812.556</v>
+        <v>9096.832</v>
       </c>
       <c r="G33">
         <v>279.4</v>
@@ -4127,37 +4127,37 @@
         <v>562.6</v>
       </c>
       <c r="M33">
-        <v>1769.5612448</v>
+        <v>1826.6438656</v>
       </c>
       <c r="N33">
-        <v>-1206.9612448</v>
+        <v>-1264.0438656</v>
       </c>
       <c r="O33">
-        <v>-265.531473856</v>
+        <v>-278.089650432</v>
       </c>
       <c r="P33">
-        <v>-941.4297709440002</v>
+        <v>-985.954215168</v>
       </c>
       <c r="Q33">
-        <v>-789.0297709440002</v>
+        <v>-833.554215168</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1032172171662887</v>
+        <v>0.1040615880069694</v>
       </c>
       <c r="T33">
-        <v>1.326032729013596</v>
+        <v>1.34553321032262</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.06994502188817375</v>
+        <v>0.06775923995416833</v>
       </c>
       <c r="W33">
-        <v>0.1867550396048547</v>
+        <v>0.187193944617203</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.317931917673517</v>
+        <v>0.3079965452462197</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4173,22 +4173,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1306639421222442</v>
+        <v>0.1322139421222442</v>
       </c>
       <c r="C34">
-        <v>4258.768355585333</v>
+        <v>3739.945590868994</v>
       </c>
       <c r="D34">
-        <v>13076.20035558533</v>
+        <v>12841.653590869</v>
       </c>
       <c r="E34">
-        <v>6965.432000000001</v>
+        <v>7249.708000000002</v>
       </c>
       <c r="F34">
-        <v>9096.832</v>
+        <v>9381.108000000002</v>
       </c>
       <c r="G34">
         <v>279.4</v>
@@ -4209,37 +4209,37 @@
         <v>562.6</v>
       </c>
       <c r="M34">
-        <v>1826.6438656</v>
+        <v>1883.726486400001</v>
       </c>
       <c r="N34">
-        <v>-1264.0438656</v>
+        <v>-1321.1264864</v>
       </c>
       <c r="O34">
-        <v>-278.089650432</v>
+        <v>-290.6478270080001</v>
       </c>
       <c r="P34">
-        <v>-985.954215168</v>
+        <v>-1030.478659392</v>
       </c>
       <c r="Q34">
-        <v>-833.554215168</v>
+        <v>-878.0786593920003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1040615880069694</v>
+        <v>0.104931163947372</v>
       </c>
       <c r="T34">
-        <v>1.34553321032262</v>
+        <v>1.365615795551316</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.06775923995416833</v>
+        <v>0.06570592965252685</v>
       </c>
       <c r="W34">
-        <v>0.187193944617203</v>
+        <v>0.1876062493257726</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3079965452462197</v>
+        <v>0.2986633166023949</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4255,22 +4255,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1322139421222442</v>
+        <v>0.1337639421222442</v>
       </c>
       <c r="C35">
-        <v>3739.945590868994</v>
+        <v>3229.38865591288</v>
       </c>
       <c r="D35">
-        <v>12841.653590869</v>
+        <v>12615.37265591288</v>
       </c>
       <c r="E35">
-        <v>7249.708000000002</v>
+        <v>7533.984000000002</v>
       </c>
       <c r="F35">
-        <v>9381.108000000002</v>
+        <v>9665.384000000002</v>
       </c>
       <c r="G35">
         <v>279.4</v>
@@ -4291,37 +4291,37 @@
         <v>562.6</v>
       </c>
       <c r="M35">
-        <v>1883.726486400001</v>
+        <v>1940.8091072</v>
       </c>
       <c r="N35">
-        <v>-1321.1264864</v>
+        <v>-1378.2091072</v>
       </c>
       <c r="O35">
-        <v>-290.6478270080001</v>
+        <v>-303.2060035840001</v>
       </c>
       <c r="P35">
-        <v>-1030.478659392</v>
+        <v>-1075.003103616</v>
       </c>
       <c r="Q35">
-        <v>-878.0786593920003</v>
+        <v>-922.6031036160003</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.104931163947372</v>
+        <v>0.1058270906738473</v>
       </c>
       <c r="T35">
-        <v>1.365615795551316</v>
+        <v>1.38630694396876</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.06570592965252685</v>
+        <v>0.06377340230980548</v>
       </c>
       <c r="W35">
-        <v>0.1876062493257726</v>
+        <v>0.1879943008161911</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2986633166023949</v>
+        <v>0.2898791014082067</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4337,22 +4337,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1337639421222442</v>
+        <v>0.1353139421222442</v>
       </c>
       <c r="C36">
-        <v>3229.38865591288</v>
+        <v>2726.668163880993</v>
       </c>
       <c r="D36">
-        <v>12615.37265591288</v>
+        <v>12396.928163881</v>
       </c>
       <c r="E36">
-        <v>7533.984000000002</v>
+        <v>7818.260000000002</v>
       </c>
       <c r="F36">
-        <v>9665.384000000002</v>
+        <v>9949.660000000002</v>
       </c>
       <c r="G36">
         <v>279.4</v>
@@ -4373,37 +4373,37 @@
         <v>562.6</v>
       </c>
       <c r="M36">
-        <v>1940.8091072</v>
+        <v>1997.891728</v>
       </c>
       <c r="N36">
-        <v>-1378.2091072</v>
+        <v>-1435.291728</v>
       </c>
       <c r="O36">
-        <v>-303.2060035840001</v>
+        <v>-315.76418016</v>
       </c>
       <c r="P36">
-        <v>-1075.003103616</v>
+        <v>-1119.52754784</v>
       </c>
       <c r="Q36">
-        <v>-922.6031036160003</v>
+        <v>-967.1275478400001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1058270906738473</v>
+        <v>0.1067505843765219</v>
       </c>
       <c r="T36">
-        <v>1.38630694396876</v>
+        <v>1.40763474310674</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.06377340230980548</v>
+        <v>0.0619513051009539</v>
       </c>
       <c r="W36">
-        <v>0.1879943008161911</v>
+        <v>0.1883601779357285</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2898791014082067</v>
+        <v>0.2815968413679723</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4419,22 +4419,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1353139421222442</v>
+        <v>0.1368639421222442</v>
       </c>
       <c r="C37">
-        <v>2726.668163880993</v>
+        <v>2231.383962322787</v>
       </c>
       <c r="D37">
-        <v>12396.928163881</v>
+        <v>12185.91996232279</v>
       </c>
       <c r="E37">
-        <v>7818.260000000002</v>
+        <v>8102.536000000002</v>
       </c>
       <c r="F37">
-        <v>9949.660000000002</v>
+        <v>10233.936</v>
       </c>
       <c r="G37">
         <v>279.4</v>
@@ -4455,37 +4455,37 @@
         <v>562.6</v>
       </c>
       <c r="M37">
-        <v>1997.891728</v>
+        <v>2054.9743488</v>
       </c>
       <c r="N37">
-        <v>-1435.291728</v>
+        <v>-1492.3743488</v>
       </c>
       <c r="O37">
-        <v>-315.76418016</v>
+        <v>-328.3223567360001</v>
       </c>
       <c r="P37">
-        <v>-1119.52754784</v>
+        <v>-1164.051992064</v>
       </c>
       <c r="Q37">
-        <v>-967.1275478400001</v>
+        <v>-1011.651992064</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1067505843765219</v>
+        <v>0.107702937257405</v>
       </c>
       <c r="T37">
-        <v>1.40763474310674</v>
+        <v>1.429629035967783</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.0619513051009539</v>
+        <v>0.06023043551481629</v>
       </c>
       <c r="W37">
-        <v>0.1883601779357285</v>
+        <v>0.1887057285486249</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2815968413679723</v>
+        <v>0.2737747068855285</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4501,22 +4501,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1368639421222442</v>
+        <v>0.1384139421222442</v>
       </c>
       <c r="C38">
-        <v>2231.383962322789</v>
+        <v>1743.162686819134</v>
       </c>
       <c r="D38">
-        <v>12185.91996232279</v>
+        <v>11981.97468681914</v>
       </c>
       <c r="E38">
-        <v>8102.536</v>
+        <v>8386.812000000002</v>
       </c>
       <c r="F38">
-        <v>10233.936</v>
+        <v>10518.212</v>
       </c>
       <c r="G38">
         <v>279.4</v>
@@ -4537,37 +4537,37 @@
         <v>562.6</v>
       </c>
       <c r="M38">
-        <v>2054.9743488</v>
+        <v>2112.0569696</v>
       </c>
       <c r="N38">
-        <v>-1492.3743488</v>
+        <v>-1549.4569696</v>
       </c>
       <c r="O38">
-        <v>-328.322356736</v>
+        <v>-340.8805333120001</v>
       </c>
       <c r="P38">
-        <v>-1164.051992064</v>
+        <v>-1208.576436288</v>
       </c>
       <c r="Q38">
-        <v>-1011.651992064</v>
+        <v>-1056.176436288</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.107702937257405</v>
+        <v>0.1086855235630781</v>
       </c>
       <c r="T38">
-        <v>1.429629035967783</v>
+        <v>1.452321560348224</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.0602304355148163</v>
+        <v>0.05860258590630774</v>
       </c>
       <c r="W38">
-        <v>0.1887057285486249</v>
+        <v>0.1890326007500134</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2737747068855285</v>
+        <v>0.2663753904832169</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4583,22 +4583,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1384139421222442</v>
+        <v>0.1399639421222442</v>
       </c>
       <c r="C39">
-        <v>1743.162686819134</v>
+        <v>1261.655556239883</v>
       </c>
       <c r="D39">
-        <v>11981.97468681914</v>
+        <v>11784.74355623988</v>
       </c>
       <c r="E39">
-        <v>8386.812000000002</v>
+        <v>8671.088000000002</v>
       </c>
       <c r="F39">
-        <v>10518.212</v>
+        <v>10802.488</v>
       </c>
       <c r="G39">
         <v>279.4</v>
@@ -4619,37 +4619,37 @@
         <v>562.6</v>
       </c>
       <c r="M39">
-        <v>2112.0569696</v>
+        <v>2169.1395904</v>
       </c>
       <c r="N39">
-        <v>-1549.4569696</v>
+        <v>-1606.5395904</v>
       </c>
       <c r="O39">
-        <v>-340.8805333120001</v>
+        <v>-353.4387098880001</v>
       </c>
       <c r="P39">
-        <v>-1208.576436288</v>
+        <v>-1253.100880512</v>
       </c>
       <c r="Q39">
-        <v>-1056.176436288</v>
+        <v>-1100.700880512</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1086855235630781</v>
+        <v>0.1096998062011923</v>
       </c>
       <c r="T39">
-        <v>1.452321560348224</v>
+        <v>1.475746101644163</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.05860258590630774</v>
+        <v>0.05706041259298385</v>
       </c>
       <c r="W39">
-        <v>0.1890326007500134</v>
+        <v>0.1893422691513288</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2663753904832169</v>
+        <v>0.2593655117862902</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4665,22 +4665,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1399639421222442</v>
+        <v>0.1415139421222442</v>
       </c>
       <c r="C40">
-        <v>1261.655556239883</v>
+        <v>786.5363822241015</v>
       </c>
       <c r="D40">
-        <v>11784.74355623988</v>
+        <v>11593.9003822241</v>
       </c>
       <c r="E40">
-        <v>8671.088000000002</v>
+        <v>8955.364000000001</v>
       </c>
       <c r="F40">
-        <v>10802.488</v>
+        <v>11086.764</v>
       </c>
       <c r="G40">
         <v>279.4</v>
@@ -4701,37 +4701,37 @@
         <v>562.6</v>
       </c>
       <c r="M40">
-        <v>2169.1395904</v>
+        <v>2226.2222112</v>
       </c>
       <c r="N40">
-        <v>-1606.5395904</v>
+        <v>-1663.6222112</v>
       </c>
       <c r="O40">
-        <v>-353.4387098880001</v>
+        <v>-365.9968864640001</v>
       </c>
       <c r="P40">
-        <v>-1253.100880512</v>
+        <v>-1297.625324736</v>
       </c>
       <c r="Q40">
-        <v>-1100.700880512</v>
+        <v>-1145.225324736</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1096998062011923</v>
+        <v>0.1107473440077692</v>
       </c>
       <c r="T40">
-        <v>1.475746101644163</v>
+        <v>1.49993866068751</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05706041259298385</v>
+        <v>0.05559732509059964</v>
       </c>
       <c r="W40">
-        <v>0.1893422691513288</v>
+        <v>0.1896360571218076</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2593655117862902</v>
+        <v>0.2527151140481801</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4747,22 +4747,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1415139421222442</v>
+        <v>0.1430639421222442</v>
       </c>
       <c r="C41">
-        <v>786.5363822241015</v>
+        <v>317.4997689861393</v>
       </c>
       <c r="D41">
-        <v>11593.9003822241</v>
+        <v>11409.13976898614</v>
       </c>
       <c r="E41">
-        <v>8955.364000000001</v>
+        <v>9239.640000000001</v>
       </c>
       <c r="F41">
-        <v>11086.764</v>
+        <v>11371.04</v>
       </c>
       <c r="G41">
         <v>279.4</v>
@@ -4783,37 +4783,37 @@
         <v>562.6</v>
       </c>
       <c r="M41">
-        <v>2226.2222112</v>
+        <v>2283.304832</v>
       </c>
       <c r="N41">
-        <v>-1663.6222112</v>
+        <v>-1720.704832</v>
       </c>
       <c r="O41">
-        <v>-365.9968864640001</v>
+        <v>-378.5550630400001</v>
       </c>
       <c r="P41">
-        <v>-1297.625324736</v>
+        <v>-1342.14976896</v>
       </c>
       <c r="Q41">
-        <v>-1145.225324736</v>
+        <v>-1189.74976896</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1107473440077692</v>
+        <v>0.111829799741232</v>
       </c>
       <c r="T41">
-        <v>1.49993866068751</v>
+        <v>1.524937638365636</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05559732509059964</v>
+        <v>0.05420739196333466</v>
       </c>
       <c r="W41">
-        <v>0.1896360571218076</v>
+        <v>0.1899151556937624</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2527151140481801</v>
+        <v>0.2463972361969756</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1430639421222442</v>
+        <v>0.1446139421222442</v>
       </c>
       <c r="C42">
-        <v>317.4997689861393</v>
+        <v>-145.7405174508003</v>
       </c>
       <c r="D42">
-        <v>11409.13976898614</v>
+        <v>11230.1754825492</v>
       </c>
       <c r="E42">
-        <v>9239.640000000001</v>
+        <v>9523.916000000003</v>
       </c>
       <c r="F42">
-        <v>11371.04</v>
+        <v>11655.316</v>
       </c>
       <c r="G42">
         <v>279.4</v>
@@ -4865,37 +4865,37 @@
         <v>562.6</v>
       </c>
       <c r="M42">
-        <v>2283.304832</v>
+        <v>2340.387452800001</v>
       </c>
       <c r="N42">
-        <v>-1720.704832</v>
+        <v>-1777.787452800001</v>
       </c>
       <c r="O42">
-        <v>-378.5550630400001</v>
+        <v>-391.1132396160002</v>
       </c>
       <c r="P42">
-        <v>-1342.14976896</v>
+        <v>-1386.674213184001</v>
       </c>
       <c r="Q42">
-        <v>-1189.74976896</v>
+        <v>-1234.274213184</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.111829799741232</v>
+        <v>0.1129489488893885</v>
       </c>
       <c r="T42">
-        <v>1.524937638365636</v>
+        <v>1.5507840390159</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05420739196333466</v>
+        <v>0.0528852604520338</v>
       </c>
       <c r="W42">
-        <v>0.1899151556937624</v>
+        <v>0.1901806397012316</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2463972361969756</v>
+        <v>0.2403875475092445</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4911,22 +4911,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1446139421222442</v>
+        <v>0.1461639421222442</v>
       </c>
       <c r="C43">
-        <v>-145.7405174508003</v>
+        <v>-603.4530289097656</v>
       </c>
       <c r="D43">
-        <v>11230.1754825492</v>
+        <v>11056.73897109024</v>
       </c>
       <c r="E43">
-        <v>9523.916000000003</v>
+        <v>9808.192000000003</v>
       </c>
       <c r="F43">
-        <v>11655.316</v>
+        <v>11939.592</v>
       </c>
       <c r="G43">
         <v>279.4</v>
@@ -4947,37 +4947,37 @@
         <v>562.6</v>
       </c>
       <c r="M43">
-        <v>2340.387452800001</v>
+        <v>2397.4700736</v>
       </c>
       <c r="N43">
-        <v>-1777.787452800001</v>
+        <v>-1834.870073600001</v>
       </c>
       <c r="O43">
-        <v>-391.1132396160002</v>
+        <v>-403.6714161920001</v>
       </c>
       <c r="P43">
-        <v>-1386.674213184001</v>
+        <v>-1431.198657408</v>
       </c>
       <c r="Q43">
-        <v>-1234.274213184</v>
+        <v>-1278.798657408001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1129489488893885</v>
+        <v>0.1141066893874814</v>
       </c>
       <c r="T43">
-        <v>1.5507840390159</v>
+        <v>1.577521694861002</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.0528852604520338</v>
+        <v>0.05162608758412824</v>
       </c>
       <c r="W43">
-        <v>0.1901806397012316</v>
+        <v>0.1904334816131071</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2403875475092445</v>
+        <v>0.2346640344733102</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1461639421222442</v>
+        <v>0.1477139421222441</v>
       </c>
       <c r="C44">
-        <v>-603.4530289097638</v>
+        <v>-1055.889979691481</v>
       </c>
       <c r="D44">
-        <v>11056.73897109024</v>
+        <v>10888.57802030852</v>
       </c>
       <c r="E44">
-        <v>9808.192000000001</v>
+        <v>10092.468</v>
       </c>
       <c r="F44">
-        <v>11939.592</v>
+        <v>12223.868</v>
       </c>
       <c r="G44">
         <v>279.4</v>
@@ -5029,37 +5029,37 @@
         <v>562.6</v>
       </c>
       <c r="M44">
-        <v>2397.4700736</v>
+        <v>2454.5526944</v>
       </c>
       <c r="N44">
-        <v>-1834.8700736</v>
+        <v>-1891.9526944</v>
       </c>
       <c r="O44">
-        <v>-403.671416192</v>
+        <v>-416.2295927680001</v>
       </c>
       <c r="P44">
-        <v>-1431.198657408</v>
+        <v>-1475.723101632</v>
       </c>
       <c r="Q44">
-        <v>-1278.798657408</v>
+        <v>-1323.323101632</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1141066893874814</v>
+        <v>0.1153050523591916</v>
       </c>
       <c r="T44">
-        <v>1.577521694861002</v>
+        <v>1.60519751406909</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.05162608758412825</v>
+        <v>0.05042548089612527</v>
       </c>
       <c r="W44">
-        <v>0.1904334816131071</v>
+        <v>0.190674563436058</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2346640344733102</v>
+        <v>0.2292067313460239</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5075,22 +5075,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1477139421222441</v>
+        <v>0.1492639421222442</v>
       </c>
       <c r="C45">
-        <v>-1055.889979691481</v>
+        <v>-1503.288470341775</v>
       </c>
       <c r="D45">
-        <v>10888.57802030852</v>
+        <v>10725.45552965823</v>
       </c>
       <c r="E45">
-        <v>10092.468</v>
+        <v>10376.744</v>
       </c>
       <c r="F45">
-        <v>12223.868</v>
+        <v>12508.144</v>
       </c>
       <c r="G45">
         <v>279.4</v>
@@ -5111,37 +5111,37 @@
         <v>562.6</v>
       </c>
       <c r="M45">
-        <v>2454.5526944</v>
+        <v>2511.6353152</v>
       </c>
       <c r="N45">
-        <v>-1891.9526944</v>
+        <v>-1949.0353152</v>
       </c>
       <c r="O45">
-        <v>-416.2295927680001</v>
+        <v>-428.7877693440001</v>
       </c>
       <c r="P45">
-        <v>-1475.723101632</v>
+        <v>-1520.247545856</v>
       </c>
       <c r="Q45">
-        <v>-1323.323101632</v>
+        <v>-1367.847545856</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1153050523591916</v>
+        <v>0.1165462140084629</v>
       </c>
       <c r="T45">
-        <v>1.60519751406909</v>
+        <v>1.633861755391752</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05042548089612527</v>
+        <v>0.04927944723939515</v>
       </c>
       <c r="W45">
-        <v>0.190674563436058</v>
+        <v>0.1909046869943295</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2292067313460239</v>
+        <v>0.223997487451796</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5157,22 +5157,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1492639421222442</v>
+        <v>0.1508139421222442</v>
       </c>
       <c r="C46">
-        <v>-1503.288470341775</v>
+        <v>-1945.871603042482</v>
       </c>
       <c r="D46">
-        <v>10725.45552965823</v>
+        <v>10567.14839695752</v>
       </c>
       <c r="E46">
-        <v>10376.744</v>
+        <v>10661.02</v>
       </c>
       <c r="F46">
-        <v>12508.144</v>
+        <v>12792.42</v>
       </c>
       <c r="G46">
         <v>279.4</v>
@@ -5193,37 +5193,37 @@
         <v>562.6</v>
       </c>
       <c r="M46">
-        <v>2511.6353152</v>
+        <v>2568.717936</v>
       </c>
       <c r="N46">
-        <v>-1949.0353152</v>
+        <v>-2006.117936000001</v>
       </c>
       <c r="O46">
-        <v>-428.7877693440001</v>
+        <v>-441.3459459200001</v>
       </c>
       <c r="P46">
-        <v>-1520.247545856</v>
+        <v>-1564.77199008</v>
       </c>
       <c r="Q46">
-        <v>-1367.847545856</v>
+        <v>-1412.371990080001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1165462140084629</v>
+        <v>0.1178325088086167</v>
       </c>
       <c r="T46">
-        <v>1.633861755391752</v>
+        <v>1.663568332762511</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.04927944723939515</v>
+        <v>0.04818434841185303</v>
       </c>
       <c r="W46">
-        <v>0.1909046869943295</v>
+        <v>0.1911245828388999</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.223997487451796</v>
+        <v>0.2190197655084228</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5239,22 +5239,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1508139421222442</v>
+        <v>0.1523639421222442</v>
       </c>
       <c r="C47">
-        <v>-1945.871603042482</v>
+        <v>-2383.849499660526</v>
       </c>
       <c r="D47">
-        <v>10567.14839695752</v>
+        <v>10413.44650033948</v>
       </c>
       <c r="E47">
-        <v>10661.02</v>
+        <v>10945.296</v>
       </c>
       <c r="F47">
-        <v>12792.42</v>
+        <v>13076.696</v>
       </c>
       <c r="G47">
         <v>279.4</v>
@@ -5275,37 +5275,37 @@
         <v>562.6</v>
       </c>
       <c r="M47">
-        <v>2568.717936</v>
+        <v>2625.8005568</v>
       </c>
       <c r="N47">
-        <v>-2006.117936000001</v>
+        <v>-2063.2005568</v>
       </c>
       <c r="O47">
-        <v>-441.3459459200001</v>
+        <v>-453.9041224960001</v>
       </c>
       <c r="P47">
-        <v>-1564.77199008</v>
+        <v>-1609.296434304</v>
       </c>
       <c r="Q47">
-        <v>-1412.371990080001</v>
+        <v>-1456.896434304</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1178325088086167</v>
+        <v>0.1191664441569245</v>
       </c>
       <c r="T47">
-        <v>1.663568332762511</v>
+        <v>1.694375153739595</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.04818434841185303</v>
+        <v>0.04713686257681274</v>
       </c>
       <c r="W47">
-        <v>0.1911245828388999</v>
+        <v>0.191334917994576</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2190197655084228</v>
+        <v>0.2142584662582397</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5321,22 +5321,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1523639421222442</v>
+        <v>0.1539139421222442</v>
       </c>
       <c r="C48">
-        <v>-2383.849499660526</v>
+        <v>-2817.420232224025</v>
       </c>
       <c r="D48">
-        <v>10413.44650033948</v>
+        <v>10264.15176777598</v>
       </c>
       <c r="E48">
-        <v>10945.296</v>
+        <v>11229.572</v>
       </c>
       <c r="F48">
-        <v>13076.696</v>
+        <v>13360.972</v>
       </c>
       <c r="G48">
         <v>279.4</v>
@@ -5357,37 +5357,37 @@
         <v>562.6</v>
       </c>
       <c r="M48">
-        <v>2625.8005568</v>
+        <v>2682.8831776</v>
       </c>
       <c r="N48">
-        <v>-2063.2005568</v>
+        <v>-2120.2831776</v>
       </c>
       <c r="O48">
-        <v>-453.9041224960001</v>
+        <v>-466.4622990720001</v>
       </c>
       <c r="P48">
-        <v>-1609.296434304</v>
+        <v>-1653.820878528</v>
       </c>
       <c r="Q48">
-        <v>-1456.896434304</v>
+        <v>-1501.420878528</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1191664441569245</v>
+        <v>0.1205507166881872</v>
       </c>
       <c r="T48">
-        <v>1.694375153739595</v>
+        <v>1.726344496262984</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.04713686257681274</v>
+        <v>0.04613395060709333</v>
       </c>
       <c r="W48">
-        <v>0.191334917994576</v>
+        <v>0.1915363027180957</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2142584662582397</v>
+        <v>0.2096997754867879</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5403,22 +5403,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1539139421222442</v>
+        <v>0.1554639421222442</v>
       </c>
       <c r="C49">
-        <v>-2817.420232224025</v>
+        <v>-3246.770674489817</v>
       </c>
       <c r="D49">
-        <v>10264.15176777598</v>
+        <v>10119.07732551018</v>
       </c>
       <c r="E49">
-        <v>11229.572</v>
+        <v>11513.848</v>
       </c>
       <c r="F49">
-        <v>13360.972</v>
+        <v>13645.248</v>
       </c>
       <c r="G49">
         <v>279.4</v>
@@ -5439,37 +5439,37 @@
         <v>562.6</v>
       </c>
       <c r="M49">
-        <v>2682.8831776</v>
+        <v>2739.9657984</v>
       </c>
       <c r="N49">
-        <v>-2120.2831776</v>
+        <v>-2177.365798400001</v>
       </c>
       <c r="O49">
-        <v>-466.4622990720001</v>
+        <v>-479.0204756480001</v>
       </c>
       <c r="P49">
-        <v>-1653.820878528</v>
+        <v>-1698.345322752</v>
       </c>
       <c r="Q49">
-        <v>-1501.420878528</v>
+        <v>-1545.945322752</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1205507166881872</v>
+        <v>0.1219882304706523</v>
       </c>
       <c r="T49">
-        <v>1.726344496262984</v>
+        <v>1.759543428883426</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.04613395060709333</v>
+        <v>0.04517282663611221</v>
       </c>
       <c r="W49">
-        <v>0.1915363027180957</v>
+        <v>0.1917292964114687</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2096997754867879</v>
+        <v>0.2053310301641463</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5485,22 +5485,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1554639421222442</v>
+        <v>0.1570139421222441</v>
       </c>
       <c r="C50">
-        <v>-3246.770674489817</v>
+        <v>-3672.077282300663</v>
       </c>
       <c r="D50">
-        <v>10119.07732551018</v>
+        <v>9978.046717699339</v>
       </c>
       <c r="E50">
-        <v>11513.848</v>
+        <v>11798.124</v>
       </c>
       <c r="F50">
-        <v>13645.248</v>
+        <v>13929.524</v>
       </c>
       <c r="G50">
         <v>279.4</v>
@@ -5521,37 +5521,37 @@
         <v>562.6</v>
       </c>
       <c r="M50">
-        <v>2739.9657984</v>
+        <v>2797.0484192</v>
       </c>
       <c r="N50">
-        <v>-2177.365798400001</v>
+        <v>-2234.4484192</v>
       </c>
       <c r="O50">
-        <v>-479.0204756480001</v>
+        <v>-491.5786522240001</v>
       </c>
       <c r="P50">
-        <v>-1698.345322752</v>
+        <v>-1742.869766976</v>
       </c>
       <c r="Q50">
-        <v>-1545.945322752</v>
+        <v>-1590.469766976</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1219882304706523</v>
+        <v>0.1234821173426259</v>
       </c>
       <c r="T50">
-        <v>1.759543428883426</v>
+        <v>1.794044280430159</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.04517282663611221</v>
+        <v>0.04425093221496706</v>
       </c>
       <c r="W50">
-        <v>0.1917292964114687</v>
+        <v>0.1919144128112346</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2053310301641463</v>
+        <v>0.2011406009771229</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5567,22 +5567,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1570139421222441</v>
+        <v>0.1761942751123365</v>
       </c>
       <c r="C51">
-        <v>-3672.077282300663</v>
+        <v>-5424.073076527004</v>
       </c>
       <c r="D51">
-        <v>9978.046717699339</v>
+        <v>8510.326923472998</v>
       </c>
       <c r="E51">
-        <v>11798.124</v>
+        <v>12082.4</v>
       </c>
       <c r="F51">
-        <v>13929.524</v>
+        <v>14213.8</v>
       </c>
       <c r="G51">
         <v>279.4</v>
@@ -5603,45 +5603,45 @@
         <v>562.6</v>
       </c>
       <c r="M51">
-        <v>2797.0484192</v>
+        <v>3351.61404</v>
       </c>
       <c r="N51">
-        <v>-2234.4484192</v>
+        <v>-2789.01404</v>
       </c>
       <c r="O51">
-        <v>-491.5786522240001</v>
+        <v>-613.5830888000002</v>
       </c>
       <c r="P51">
-        <v>-1742.869766976</v>
+        <v>-2175.4309512</v>
       </c>
       <c r="Q51">
-        <v>-1590.469766976</v>
+        <v>-2023.0309512</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1234821173426259</v>
+        <v>0.125296425669663</v>
       </c>
       <c r="T51">
-        <v>1.794044280430159</v>
+        <v>1.835945165581132</v>
       </c>
       <c r="U51">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04425093221496706</v>
+        <v>0.03692907313396981</v>
       </c>
       <c r="W51">
-        <v>0.1919144128112346</v>
+        <v>0.2270921245550099</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y51">
-        <v>0.2011406009771229</v>
+        <v>0.1678594233362264</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5649,22 +5649,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1761942751123365</v>
+        <v>0.1780942751123365</v>
       </c>
       <c r="C52">
-        <v>-5424.073076527004</v>
+        <v>-5830.573724123193</v>
       </c>
       <c r="D52">
-        <v>8510.326923472998</v>
+        <v>8388.102275876809</v>
       </c>
       <c r="E52">
-        <v>12082.4</v>
+        <v>12366.676</v>
       </c>
       <c r="F52">
-        <v>14213.8</v>
+        <v>14498.076</v>
       </c>
       <c r="G52">
         <v>279.4</v>
@@ -5685,37 +5685,37 @@
         <v>562.6</v>
       </c>
       <c r="M52">
-        <v>3351.61404</v>
+        <v>3418.6463208</v>
       </c>
       <c r="N52">
-        <v>-2789.01404</v>
+        <v>-2856.046320800001</v>
       </c>
       <c r="O52">
-        <v>-613.5830888000002</v>
+        <v>-628.3301905760002</v>
       </c>
       <c r="P52">
-        <v>-2175.4309512</v>
+        <v>-2227.716130224</v>
       </c>
       <c r="Q52">
-        <v>-2023.0309512</v>
+        <v>-2075.316130224</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.125296425669663</v>
+        <v>0.1269188017037378</v>
       </c>
       <c r="T52">
-        <v>1.835945165581132</v>
+        <v>1.873413434266462</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03692907313396981</v>
+        <v>0.03620497366075471</v>
       </c>
       <c r="W52">
-        <v>0.2270921245550099</v>
+        <v>0.2272628672107941</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1678594233362264</v>
+        <v>0.1645680620943395</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5731,22 +5731,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1780942751123365</v>
+        <v>0.1799942751123365</v>
       </c>
       <c r="C53">
-        <v>-5830.573724123193</v>
+        <v>-6233.613317509156</v>
       </c>
       <c r="D53">
-        <v>8388.102275876809</v>
+        <v>8269.338682490845</v>
       </c>
       <c r="E53">
-        <v>12366.676</v>
+        <v>12650.952</v>
       </c>
       <c r="F53">
-        <v>14498.076</v>
+        <v>14782.352</v>
       </c>
       <c r="G53">
         <v>279.4</v>
@@ -5767,37 +5767,37 @@
         <v>562.6</v>
       </c>
       <c r="M53">
-        <v>3418.6463208</v>
+        <v>3485.678601600001</v>
       </c>
       <c r="N53">
-        <v>-2856.046320800001</v>
+        <v>-2923.078601600001</v>
       </c>
       <c r="O53">
-        <v>-628.3301905760002</v>
+        <v>-643.0772923520002</v>
       </c>
       <c r="P53">
-        <v>-2227.716130224</v>
+        <v>-2280.001309248</v>
       </c>
       <c r="Q53">
-        <v>-2075.316130224</v>
+        <v>-2127.601309248</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1269188017037378</v>
+        <v>0.1286087767392323</v>
       </c>
       <c r="T53">
-        <v>1.873413434266462</v>
+        <v>1.912442880813679</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03620497366075471</v>
+        <v>0.03550872416727865</v>
       </c>
       <c r="W53">
-        <v>0.2272628672107941</v>
+        <v>0.2274270428413557</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1645680620943395</v>
+        <v>0.1614032916694484</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5813,22 +5813,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1799942751123365</v>
+        <v>0.1818942751123365</v>
       </c>
       <c r="C54">
-        <v>-6233.613317509156</v>
+        <v>-6633.336815089522</v>
       </c>
       <c r="D54">
-        <v>8269.338682490845</v>
+        <v>8153.891184910481</v>
       </c>
       <c r="E54">
-        <v>12650.952</v>
+        <v>12935.228</v>
       </c>
       <c r="F54">
-        <v>14782.352</v>
+        <v>15066.628</v>
       </c>
       <c r="G54">
         <v>279.4</v>
@@ -5849,37 +5849,37 @@
         <v>562.6</v>
       </c>
       <c r="M54">
-        <v>3485.678601600001</v>
+        <v>3552.710882400001</v>
       </c>
       <c r="N54">
-        <v>-2923.078601600001</v>
+        <v>-2990.110882400001</v>
       </c>
       <c r="O54">
-        <v>-643.0772923520002</v>
+        <v>-657.8243941280001</v>
       </c>
       <c r="P54">
-        <v>-2280.001309248</v>
+        <v>-2332.286488272</v>
       </c>
       <c r="Q54">
-        <v>-2127.601309248</v>
+        <v>-2179.886488272</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1286087767392323</v>
+        <v>0.1303706656060245</v>
       </c>
       <c r="T54">
-        <v>1.912442880813679</v>
+        <v>1.953133154873545</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03550872416727865</v>
+        <v>0.03483874823959415</v>
       </c>
       <c r="W54">
-        <v>0.2274270428413557</v>
+        <v>0.2275850231651037</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1614032916694484</v>
+        <v>0.1583579465436098</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5895,22 +5895,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1818942751123365</v>
+        <v>0.1837942751123365</v>
       </c>
       <c r="C55">
-        <v>-6633.336815089522</v>
+        <v>-7029.881191721219</v>
       </c>
       <c r="D55">
-        <v>8153.891184910481</v>
+        <v>8041.622808278783</v>
       </c>
       <c r="E55">
-        <v>12935.228</v>
+        <v>13219.504</v>
       </c>
       <c r="F55">
-        <v>15066.628</v>
+        <v>15350.904</v>
       </c>
       <c r="G55">
         <v>279.4</v>
@@ -5931,37 +5931,37 @@
         <v>562.6</v>
       </c>
       <c r="M55">
-        <v>3552.710882400001</v>
+        <v>3619.743163200001</v>
       </c>
       <c r="N55">
-        <v>-2990.110882400001</v>
+        <v>-3057.143163200001</v>
       </c>
       <c r="O55">
-        <v>-657.8243941280001</v>
+        <v>-672.5714959040001</v>
       </c>
       <c r="P55">
-        <v>-2332.286488272</v>
+        <v>-2384.571667296001</v>
       </c>
       <c r="Q55">
-        <v>-2179.886488272</v>
+        <v>-2232.171667296001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1303706656060245</v>
+        <v>0.1322091583365902</v>
       </c>
       <c r="T55">
-        <v>1.953133154873545</v>
+        <v>1.995592571283839</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03483874823959415</v>
+        <v>0.03419358623515723</v>
       </c>
       <c r="W55">
-        <v>0.2275850231651037</v>
+        <v>0.2277371523657499</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1583579465436098</v>
+        <v>0.1554253919779873</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5977,22 +5977,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1837942751123365</v>
+        <v>0.1856942751123365</v>
       </c>
       <c r="C56">
-        <v>-7029.881191721219</v>
+        <v>-7423.375980863666</v>
       </c>
       <c r="D56">
-        <v>8041.622808278783</v>
+        <v>7932.404019136336</v>
       </c>
       <c r="E56">
-        <v>13219.504</v>
+        <v>13503.78</v>
       </c>
       <c r="F56">
-        <v>15350.904</v>
+        <v>15635.18</v>
       </c>
       <c r="G56">
         <v>279.4</v>
@@ -6013,37 +6013,37 @@
         <v>562.6</v>
       </c>
       <c r="M56">
-        <v>3619.743163200001</v>
+        <v>3686.775444000001</v>
       </c>
       <c r="N56">
-        <v>-3057.143163200001</v>
+        <v>-3124.175444000001</v>
       </c>
       <c r="O56">
-        <v>-672.5714959040001</v>
+        <v>-687.3185976800002</v>
       </c>
       <c r="P56">
-        <v>-2384.571667296001</v>
+        <v>-2436.856846320001</v>
       </c>
       <c r="Q56">
-        <v>-2232.171667296001</v>
+        <v>-2284.456846320001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1322091583365902</v>
+        <v>0.1341293618551812</v>
       </c>
       <c r="T56">
-        <v>1.995592571283839</v>
+        <v>2.039939072867925</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03419358623515723</v>
+        <v>0.03357188466724527</v>
       </c>
       <c r="W56">
-        <v>0.2277371523657499</v>
+        <v>0.2278837495954636</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1554253919779873</v>
+        <v>0.1525994757602057</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1856942751123365</v>
+        <v>0.1875942751123365</v>
       </c>
       <c r="C57">
-        <v>-7423.375980863666</v>
+        <v>-7813.943773141026</v>
       </c>
       <c r="D57">
-        <v>7932.404019136336</v>
+        <v>7826.112226858976</v>
       </c>
       <c r="E57">
-        <v>13503.78</v>
+        <v>13788.056</v>
       </c>
       <c r="F57">
-        <v>15635.18</v>
+        <v>15919.456</v>
       </c>
       <c r="G57">
         <v>279.4</v>
@@ -6095,37 +6095,37 @@
         <v>562.6</v>
       </c>
       <c r="M57">
-        <v>3686.775444000001</v>
+        <v>3753.8077248</v>
       </c>
       <c r="N57">
-        <v>-3124.175444000001</v>
+        <v>-3191.207724800001</v>
       </c>
       <c r="O57">
-        <v>-687.3185976800002</v>
+        <v>-702.0656994560001</v>
       </c>
       <c r="P57">
-        <v>-2436.856846320001</v>
+        <v>-2489.142025344001</v>
       </c>
       <c r="Q57">
-        <v>-2284.456846320001</v>
+        <v>-2336.742025344</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1341293618551812</v>
+        <v>0.1361368473518898</v>
       </c>
       <c r="T57">
-        <v>2.039939072867925</v>
+        <v>2.086301324524014</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03357188466724527</v>
+        <v>0.03297238672675875</v>
       </c>
       <c r="W57">
-        <v>0.2278837495954636</v>
+        <v>0.2280251112098303</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1525994757602057</v>
+        <v>0.1498744851216307</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6141,22 +6141,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1875942751123365</v>
+        <v>0.1894942751123365</v>
       </c>
       <c r="C58">
-        <v>-7813.943773141026</v>
+        <v>-8201.700675350994</v>
       </c>
       <c r="D58">
-        <v>7826.112226858976</v>
+        <v>7722.63132464901</v>
       </c>
       <c r="E58">
-        <v>13788.056</v>
+        <v>14072.332</v>
       </c>
       <c r="F58">
-        <v>15919.456</v>
+        <v>16203.732</v>
       </c>
       <c r="G58">
         <v>279.4</v>
@@ -6177,37 +6177,37 @@
         <v>562.6</v>
       </c>
       <c r="M58">
-        <v>3753.8077248</v>
+        <v>3820.840005600001</v>
       </c>
       <c r="N58">
-        <v>-3191.207724800001</v>
+        <v>-3258.240005600001</v>
       </c>
       <c r="O58">
-        <v>-702.0656994560001</v>
+        <v>-716.8128012320002</v>
       </c>
       <c r="P58">
-        <v>-2489.142025344001</v>
+        <v>-2541.427204368001</v>
       </c>
       <c r="Q58">
-        <v>-2336.742025344</v>
+        <v>-2389.027204368001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1361368473518898</v>
+        <v>0.13823770426705</v>
       </c>
       <c r="T58">
-        <v>2.086301324524014</v>
+        <v>2.134819959978061</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03297238672675875</v>
+        <v>0.03239392380172789</v>
       </c>
       <c r="W58">
-        <v>0.2280251112098303</v>
+        <v>0.2281615127675526</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1498744851216307</v>
+        <v>0.1472451081896722</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6223,22 +6223,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1894942751123365</v>
+        <v>0.1913942751123365</v>
       </c>
       <c r="C59">
-        <v>-8201.700675350994</v>
+        <v>-8586.756733533308</v>
       </c>
       <c r="D59">
-        <v>7722.63132464901</v>
+        <v>7621.851266466694</v>
       </c>
       <c r="E59">
-        <v>14072.332</v>
+        <v>14356.608</v>
       </c>
       <c r="F59">
-        <v>16203.732</v>
+        <v>16488.008</v>
       </c>
       <c r="G59">
         <v>279.4</v>
@@ -6259,37 +6259,37 @@
         <v>562.6</v>
       </c>
       <c r="M59">
-        <v>3820.840005600001</v>
+        <v>3887.872286400001</v>
       </c>
       <c r="N59">
-        <v>-3258.240005600001</v>
+        <v>-3325.272286400001</v>
       </c>
       <c r="O59">
-        <v>-716.8128012320002</v>
+        <v>-731.5599030080001</v>
       </c>
       <c r="P59">
-        <v>-2541.427204368001</v>
+        <v>-2593.712383392</v>
       </c>
       <c r="Q59">
-        <v>-2389.027204368001</v>
+        <v>-2441.312383392</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.13823770426705</v>
+        <v>0.1404386019876941</v>
       </c>
       <c r="T59">
-        <v>2.134819959978061</v>
+        <v>2.185649006644206</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03239392380172789</v>
+        <v>0.0318354078741119</v>
       </c>
       <c r="W59">
-        <v>0.2281615127675526</v>
+        <v>0.2282932108232844</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1472451081896722</v>
+        <v>0.1447063994277813</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6305,22 +6305,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1913942751123365</v>
+        <v>0.1932942751123365</v>
       </c>
       <c r="C60">
-        <v>-8586.756733533308</v>
+        <v>-8969.216323338787</v>
       </c>
       <c r="D60">
-        <v>7621.851266466694</v>
+        <v>7523.667676661212</v>
       </c>
       <c r="E60">
-        <v>14356.608</v>
+        <v>14640.884</v>
       </c>
       <c r="F60">
-        <v>16488.008</v>
+        <v>16772.284</v>
       </c>
       <c r="G60">
         <v>279.4</v>
@@ -6341,37 +6341,37 @@
         <v>562.6</v>
       </c>
       <c r="M60">
-        <v>3887.872286400001</v>
+        <v>3954.9045672</v>
       </c>
       <c r="N60">
-        <v>-3325.272286400001</v>
+        <v>-3392.3045672</v>
       </c>
       <c r="O60">
-        <v>-731.5599030080001</v>
+        <v>-746.307004784</v>
       </c>
       <c r="P60">
-        <v>-2593.712383392</v>
+        <v>-2645.997562416</v>
       </c>
       <c r="Q60">
-        <v>-2441.312383392</v>
+        <v>-2493.597562416</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1404386019876941</v>
+        <v>0.1427468605727598</v>
       </c>
       <c r="T60">
-        <v>2.185649006644205</v>
+        <v>2.238957519001381</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0318354078741119</v>
+        <v>0.03129582468980491</v>
       </c>
       <c r="W60">
-        <v>0.2282932108232844</v>
+        <v>0.228420444538144</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6379,7 +6379,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1447063994277813</v>
+        <v>0.1422537485900224</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6387,22 +6387,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1932942751123365</v>
+        <v>0.1951942751123365</v>
       </c>
       <c r="C61">
-        <v>-8969.216323338787</v>
+        <v>-9349.178510610069</v>
       </c>
       <c r="D61">
-        <v>7523.667676661212</v>
+        <v>7427.981489389932</v>
       </c>
       <c r="E61">
-        <v>14640.884</v>
+        <v>14925.16</v>
       </c>
       <c r="F61">
-        <v>16772.284</v>
+        <v>17056.56</v>
       </c>
       <c r="G61">
         <v>279.4</v>
@@ -6423,37 +6423,37 @@
         <v>562.6</v>
       </c>
       <c r="M61">
-        <v>3954.9045672</v>
+        <v>4021.936848</v>
       </c>
       <c r="N61">
-        <v>-3392.3045672</v>
+        <v>-3459.336848</v>
       </c>
       <c r="O61">
-        <v>-746.307004784</v>
+        <v>-761.05410656</v>
       </c>
       <c r="P61">
-        <v>-2645.997562416</v>
+        <v>-2698.28274144</v>
       </c>
       <c r="Q61">
-        <v>-2493.597562416</v>
+        <v>-2545.88274144</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1427468605727598</v>
+        <v>0.1451705320870788</v>
       </c>
       <c r="T61">
-        <v>2.238957519001381</v>
+        <v>2.294931456976415</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03129582468980491</v>
+        <v>0.03077422761164151</v>
       </c>
       <c r="W61">
-        <v>0.228420444538144</v>
+        <v>0.2285434371291749</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1422537485900224</v>
+        <v>0.1398828527801886</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6469,22 +6469,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1951942751123365</v>
+        <v>0.1970942751123365</v>
       </c>
       <c r="C62">
-        <v>-9349.178510610069</v>
+        <v>-9726.737384792596</v>
       </c>
       <c r="D62">
-        <v>7427.981489389932</v>
+        <v>7334.698615207405</v>
       </c>
       <c r="E62">
-        <v>14925.16</v>
+        <v>15209.436</v>
       </c>
       <c r="F62">
-        <v>17056.56</v>
+        <v>17340.836</v>
       </c>
       <c r="G62">
         <v>279.4</v>
@@ -6505,37 +6505,37 @@
         <v>562.6</v>
       </c>
       <c r="M62">
-        <v>4021.936848</v>
+        <v>4088.9691288</v>
       </c>
       <c r="N62">
-        <v>-3459.336848</v>
+        <v>-3526.3691288</v>
       </c>
       <c r="O62">
-        <v>-761.05410656</v>
+        <v>-775.8012083360001</v>
       </c>
       <c r="P62">
-        <v>-2698.28274144</v>
+        <v>-2750.567920464</v>
       </c>
       <c r="Q62">
-        <v>-2545.88274144</v>
+        <v>-2598.167920464</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1451705320870788</v>
+        <v>0.1477184944482859</v>
       </c>
       <c r="T62">
-        <v>2.294931456976415</v>
+        <v>2.353775853309144</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03077422761164151</v>
+        <v>0.03026973207702443</v>
       </c>
       <c r="W62">
-        <v>0.2285434371291749</v>
+        <v>0.2286623971762377</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1398828527801886</v>
+        <v>0.137589691259202</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6551,22 +6551,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1970942751123365</v>
+        <v>0.1989942751123365</v>
       </c>
       <c r="C63">
-        <v>-9726.737384792596</v>
+        <v>-10101.98236753477</v>
       </c>
       <c r="D63">
-        <v>7334.698615207405</v>
+        <v>7243.729632465228</v>
       </c>
       <c r="E63">
-        <v>15209.436</v>
+        <v>15493.712</v>
       </c>
       <c r="F63">
-        <v>17340.836</v>
+        <v>17625.112</v>
       </c>
       <c r="G63">
         <v>279.4</v>
@@ -6587,37 +6587,37 @@
         <v>562.6</v>
       </c>
       <c r="M63">
-        <v>4088.9691288</v>
+        <v>4156.0014096</v>
       </c>
       <c r="N63">
-        <v>-3526.3691288</v>
+        <v>-3593.401409600001</v>
       </c>
       <c r="O63">
-        <v>-775.8012083360001</v>
+        <v>-790.5483101120001</v>
       </c>
       <c r="P63">
-        <v>-2750.567920464</v>
+        <v>-2802.853099488</v>
       </c>
       <c r="Q63">
-        <v>-2598.167920464</v>
+        <v>-2650.453099488</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1477184944482859</v>
+        <v>0.1504005600916619</v>
       </c>
       <c r="T63">
-        <v>2.353775853309144</v>
+        <v>2.415717323133069</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03026973207702443</v>
+        <v>0.02978151059191113</v>
       </c>
       <c r="W63">
-        <v>0.2286623971762377</v>
+        <v>0.2287775198024274</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.137589691259202</v>
+        <v>0.1353705026905051</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6633,22 +6633,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1989942751123365</v>
+        <v>0.2008942751123365</v>
       </c>
       <c r="C64">
-        <v>-10101.98236753477</v>
+        <v>-10474.99849860483</v>
       </c>
       <c r="D64">
-        <v>7243.729632465228</v>
+        <v>7154.989501395175</v>
       </c>
       <c r="E64">
-        <v>15493.712</v>
+        <v>15777.988</v>
       </c>
       <c r="F64">
-        <v>17625.112</v>
+        <v>17909.388</v>
       </c>
       <c r="G64">
         <v>279.4</v>
@@ -6669,37 +6669,37 @@
         <v>562.6</v>
       </c>
       <c r="M64">
-        <v>4156.0014096</v>
+        <v>4223.033690400001</v>
       </c>
       <c r="N64">
-        <v>-3593.401409600001</v>
+        <v>-3660.433690400001</v>
       </c>
       <c r="O64">
-        <v>-790.5483101120001</v>
+        <v>-805.2954118880001</v>
       </c>
       <c r="P64">
-        <v>-2802.853099488</v>
+        <v>-2855.138278512</v>
       </c>
       <c r="Q64">
-        <v>-2650.453099488</v>
+        <v>-2702.738278512</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1504005600916619</v>
+        <v>0.1532276022563014</v>
       </c>
       <c r="T64">
-        <v>2.415717323133069</v>
+        <v>2.481006980515044</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02978151059191113</v>
+        <v>0.02930878820156333</v>
       </c>
       <c r="W64">
-        <v>0.2287775198024274</v>
+        <v>0.2288889877420714</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1353705026905051</v>
+        <v>0.1332217645525606</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6715,22 +6715,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2008942751123365</v>
+        <v>0.2027942751123364</v>
       </c>
       <c r="C65">
-        <v>-10474.99849860483</v>
+        <v>-10845.86670104611</v>
       </c>
       <c r="D65">
-        <v>7154.989501395175</v>
+        <v>7068.397298953888</v>
       </c>
       <c r="E65">
-        <v>15777.988</v>
+        <v>16062.264</v>
       </c>
       <c r="F65">
-        <v>17909.388</v>
+        <v>18193.664</v>
       </c>
       <c r="G65">
         <v>279.4</v>
@@ -6751,37 +6751,37 @@
         <v>562.6</v>
       </c>
       <c r="M65">
-        <v>4223.033690400001</v>
+        <v>4290.065971200001</v>
       </c>
       <c r="N65">
-        <v>-3660.433690400001</v>
+        <v>-3727.465971200001</v>
       </c>
       <c r="O65">
-        <v>-805.2954118880001</v>
+        <v>-820.0425136640001</v>
       </c>
       <c r="P65">
-        <v>-2855.138278512</v>
+        <v>-2907.423457536001</v>
       </c>
       <c r="Q65">
-        <v>-2702.738278512</v>
+        <v>-2755.023457536</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1532276022563014</v>
+        <v>0.1562117023189764</v>
       </c>
       <c r="T65">
-        <v>2.481006980515044</v>
+        <v>2.549923841084906</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02930878820156333</v>
+        <v>0.02885083838591391</v>
       </c>
       <c r="W65">
-        <v>0.2288889877420714</v>
+        <v>0.2289969723086015</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1332217645525606</v>
+        <v>0.1311401744814268</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6797,22 +6797,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2027942751123364</v>
+        <v>0.2046942751123365</v>
       </c>
       <c r="C66">
-        <v>-10845.86670104611</v>
+        <v>-11214.66402730861</v>
       </c>
       <c r="D66">
-        <v>7068.397298953888</v>
+        <v>6983.875972691391</v>
       </c>
       <c r="E66">
-        <v>16062.264</v>
+        <v>16346.54</v>
       </c>
       <c r="F66">
-        <v>18193.664</v>
+        <v>18477.94</v>
       </c>
       <c r="G66">
         <v>279.4</v>
@@ -6833,37 +6833,37 @@
         <v>562.6</v>
       </c>
       <c r="M66">
-        <v>4290.065971200001</v>
+        <v>4357.098252000001</v>
       </c>
       <c r="N66">
-        <v>-3727.465971200001</v>
+        <v>-3794.498252000001</v>
       </c>
       <c r="O66">
-        <v>-820.0425136640001</v>
+        <v>-834.7896154400001</v>
       </c>
       <c r="P66">
-        <v>-2907.423457536001</v>
+        <v>-2959.708636560001</v>
       </c>
       <c r="Q66">
-        <v>-2755.023457536</v>
+        <v>-2807.308636560001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1562117023189764</v>
+        <v>0.1593663223852329</v>
       </c>
       <c r="T66">
-        <v>2.549923841084906</v>
+        <v>2.622778807973047</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02885083838591391</v>
+        <v>0.02840697933382292</v>
       </c>
       <c r="W66">
-        <v>0.2289969723086015</v>
+        <v>0.2291016342730846</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1311401744814268</v>
+        <v>0.1291226333355587</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6879,22 +6879,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2046942751123365</v>
+        <v>0.2065942751123365</v>
       </c>
       <c r="C67">
-        <v>-11214.66402730861</v>
+        <v>-11581.46388793016</v>
       </c>
       <c r="D67">
-        <v>6983.875972691391</v>
+        <v>6901.35211206984</v>
       </c>
       <c r="E67">
-        <v>16346.54</v>
+        <v>16630.816</v>
       </c>
       <c r="F67">
-        <v>18477.94</v>
+        <v>18762.216</v>
       </c>
       <c r="G67">
         <v>279.4</v>
@@ -6915,37 +6915,37 @@
         <v>562.6</v>
       </c>
       <c r="M67">
-        <v>4357.098252000001</v>
+        <v>4424.130532800001</v>
       </c>
       <c r="N67">
-        <v>-3794.498252000001</v>
+        <v>-3861.530532800001</v>
       </c>
       <c r="O67">
-        <v>-834.7896154400001</v>
+        <v>-849.5367172160002</v>
       </c>
       <c r="P67">
-        <v>-2959.708636560001</v>
+        <v>-3011.993815584001</v>
       </c>
       <c r="Q67">
-        <v>-2807.308636560001</v>
+        <v>-2859.593815584001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1593663223852329</v>
+        <v>0.1627065083377397</v>
       </c>
       <c r="T67">
-        <v>2.622778807973047</v>
+        <v>2.699919361148724</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02840697933382292</v>
+        <v>0.02797657055603773</v>
       </c>
       <c r="W67">
-        <v>0.2291016342730846</v>
+        <v>0.2292031246628863</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1291226333355587</v>
+        <v>0.1271662298001714</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6961,22 +6961,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2065942751123365</v>
+        <v>0.2084942751123365</v>
       </c>
       <c r="C68">
-        <v>-11581.46388793016</v>
+        <v>-11946.33626419404</v>
       </c>
       <c r="D68">
-        <v>6901.35211206984</v>
+        <v>6820.755735805964</v>
       </c>
       <c r="E68">
-        <v>16630.816</v>
+        <v>16915.092</v>
       </c>
       <c r="F68">
-        <v>18762.216</v>
+        <v>19046.492</v>
       </c>
       <c r="G68">
         <v>279.4</v>
@@ -6997,37 +6997,37 @@
         <v>562.6</v>
       </c>
       <c r="M68">
-        <v>4424.130532800001</v>
+        <v>4491.162813600001</v>
       </c>
       <c r="N68">
-        <v>-3861.530532800001</v>
+        <v>-3928.562813600001</v>
       </c>
       <c r="O68">
-        <v>-849.5367172160002</v>
+        <v>-864.2838189920002</v>
       </c>
       <c r="P68">
-        <v>-3011.993815584001</v>
+        <v>-3064.278994608001</v>
       </c>
       <c r="Q68">
-        <v>-2859.593815584001</v>
+        <v>-2911.878994608001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1627065083377397</v>
+        <v>0.1662491298025197</v>
       </c>
       <c r="T68">
-        <v>2.699919361148724</v>
+        <v>2.781735099365352</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02797657055603773</v>
+        <v>0.02755900980147</v>
       </c>
       <c r="W68">
-        <v>0.2292031246628863</v>
+        <v>0.2293015854888134</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1271662298001714</v>
+        <v>0.1252682263703182</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7043,22 +7043,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2084942751123365</v>
+        <v>0.2103942751123365</v>
       </c>
       <c r="C69">
-        <v>-11946.33626419404</v>
+        <v>-12309.34790605757</v>
       </c>
       <c r="D69">
-        <v>6820.755735805964</v>
+        <v>6742.020093942436</v>
       </c>
       <c r="E69">
-        <v>16915.092</v>
+        <v>17199.368</v>
       </c>
       <c r="F69">
-        <v>19046.492</v>
+        <v>19330.768</v>
       </c>
       <c r="G69">
         <v>279.4</v>
@@ -7079,37 +7079,37 @@
         <v>562.6</v>
       </c>
       <c r="M69">
-        <v>4491.162813600001</v>
+        <v>4558.195094400001</v>
       </c>
       <c r="N69">
-        <v>-3928.562813600001</v>
+        <v>-3995.595094400001</v>
       </c>
       <c r="O69">
-        <v>-864.2838189920002</v>
+        <v>-879.0309207680002</v>
       </c>
       <c r="P69">
-        <v>-3064.278994608001</v>
+        <v>-3116.564173632001</v>
       </c>
       <c r="Q69">
-        <v>-2911.878994608001</v>
+        <v>-2964.164173632001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1662491298025197</v>
+        <v>0.1700131651088485</v>
       </c>
       <c r="T69">
-        <v>2.781735099365352</v>
+        <v>2.86866432122052</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02755900980147</v>
+        <v>0.02715373024556603</v>
       </c>
       <c r="W69">
-        <v>0.2293015854888134</v>
+        <v>0.2293971504080956</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1252682263703182</v>
+        <v>0.1234260465707546</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7125,22 +7125,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2103942751123365</v>
+        <v>0.2122942751123365</v>
       </c>
       <c r="C70">
-        <v>-12309.34790605757</v>
+        <v>-12670.56251652839</v>
       </c>
       <c r="D70">
-        <v>6742.020093942436</v>
+        <v>6665.081483471611</v>
       </c>
       <c r="E70">
-        <v>17199.368</v>
+        <v>17483.644</v>
       </c>
       <c r="F70">
-        <v>19330.768</v>
+        <v>19615.044</v>
       </c>
       <c r="G70">
         <v>279.4</v>
@@ -7161,37 +7161,37 @@
         <v>562.6</v>
       </c>
       <c r="M70">
-        <v>4558.195094400001</v>
+        <v>4625.227375200001</v>
       </c>
       <c r="N70">
-        <v>-3995.595094400001</v>
+        <v>-4062.627375200001</v>
       </c>
       <c r="O70">
-        <v>-879.0309207680002</v>
+        <v>-893.7780225440002</v>
       </c>
       <c r="P70">
-        <v>-3116.564173632001</v>
+        <v>-3168.849352656001</v>
       </c>
       <c r="Q70">
-        <v>-2964.164173632001</v>
+        <v>-3016.449352656001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1700131651088485</v>
+        <v>0.1740200414026823</v>
       </c>
       <c r="T70">
-        <v>2.86866432122052</v>
+        <v>2.961201879969569</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02715373024556603</v>
+        <v>0.02676019792316652</v>
       </c>
       <c r="W70">
-        <v>0.2293971504080956</v>
+        <v>0.2294899453297173</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1234260465707546</v>
+        <v>0.1216372632871205</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7207,22 +7207,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2122942751123365</v>
+        <v>0.2141942751123365</v>
       </c>
       <c r="C71">
-        <v>-12670.56251652839</v>
+        <v>-13030.04092355884</v>
       </c>
       <c r="D71">
-        <v>6665.081483471611</v>
+        <v>6589.879076441158</v>
       </c>
       <c r="E71">
-        <v>17483.644</v>
+        <v>17767.92</v>
       </c>
       <c r="F71">
-        <v>19615.044</v>
+        <v>19899.32</v>
       </c>
       <c r="G71">
         <v>279.4</v>
@@ -7243,37 +7243,37 @@
         <v>562.6</v>
       </c>
       <c r="M71">
-        <v>4625.227375200001</v>
+        <v>4692.259656000001</v>
       </c>
       <c r="N71">
-        <v>-4062.627375200001</v>
+        <v>-4129.659656000001</v>
       </c>
       <c r="O71">
-        <v>-893.7780225440002</v>
+        <v>-908.5251243200001</v>
       </c>
       <c r="P71">
-        <v>-3168.849352656001</v>
+        <v>-3221.134531680001</v>
       </c>
       <c r="Q71">
-        <v>-3016.449352656001</v>
+        <v>-3068.734531680001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1740200414026823</v>
+        <v>0.1782940427827717</v>
       </c>
       <c r="T71">
-        <v>2.961201879969569</v>
+        <v>3.059908609301888</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02676019792316652</v>
+        <v>0.026377909381407</v>
       </c>
       <c r="W71">
-        <v>0.2294899453297173</v>
+        <v>0.2295800889678642</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1216372632871205</v>
+        <v>0.1198995880973046</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7289,22 +7289,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2141942751123365</v>
+        <v>0.2160942751123365</v>
       </c>
       <c r="C72">
-        <v>-13030.04092355884</v>
+        <v>-13387.84124043315</v>
       </c>
       <c r="D72">
-        <v>6589.879076441158</v>
+        <v>6516.35475956686</v>
       </c>
       <c r="E72">
-        <v>17767.92</v>
+        <v>18052.196</v>
       </c>
       <c r="F72">
-        <v>19899.32</v>
+        <v>20183.59600000001</v>
       </c>
       <c r="G72">
         <v>279.4</v>
@@ -7325,37 +7325,37 @@
         <v>562.6</v>
       </c>
       <c r="M72">
-        <v>4692.259656000001</v>
+        <v>4759.291936800001</v>
       </c>
       <c r="N72">
-        <v>-4129.659656000001</v>
+        <v>-4196.691936800001</v>
       </c>
       <c r="O72">
-        <v>-908.5251243200001</v>
+        <v>-923.2722260960002</v>
       </c>
       <c r="P72">
-        <v>-3221.134531680001</v>
+        <v>-3273.419710704001</v>
       </c>
       <c r="Q72">
-        <v>-3068.734531680001</v>
+        <v>-3121.019710704001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1782940427827717</v>
+        <v>0.1828628028787294</v>
       </c>
       <c r="T72">
-        <v>3.059908609301888</v>
+        <v>3.165422699277816</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.026377909381407</v>
+        <v>0.02600638953096465</v>
       </c>
       <c r="W72">
-        <v>0.2295800889678642</v>
+        <v>0.2296676933485985</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1198995880973046</v>
+        <v>0.1182108615043849</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7371,22 +7371,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2160942751123364</v>
+        <v>0.2179942751123364</v>
       </c>
       <c r="C73">
-        <v>-13387.84124043314</v>
+        <v>-13744.01901553629</v>
       </c>
       <c r="D73">
-        <v>6516.354759566863</v>
+        <v>6444.452984463715</v>
       </c>
       <c r="E73">
-        <v>18052.196</v>
+        <v>18336.472</v>
       </c>
       <c r="F73">
-        <v>20183.596</v>
+        <v>20467.872</v>
       </c>
       <c r="G73">
         <v>279.4</v>
@@ -7407,37 +7407,37 @@
         <v>562.6</v>
       </c>
       <c r="M73">
-        <v>4759.2919368</v>
+        <v>4826.3242176</v>
       </c>
       <c r="N73">
-        <v>-4196.6919368</v>
+        <v>-4263.7242176</v>
       </c>
       <c r="O73">
-        <v>-923.2722260959999</v>
+        <v>-938.019327872</v>
       </c>
       <c r="P73">
-        <v>-3273.419710704</v>
+        <v>-3325.704889728</v>
       </c>
       <c r="Q73">
-        <v>-3121.019710704</v>
+        <v>-3173.304889728</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1828628028787293</v>
+        <v>0.1877579029815411</v>
       </c>
       <c r="T73">
-        <v>3.165422699277814</v>
+        <v>3.278473509966307</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02600638953096465</v>
+        <v>0.02564518967636792</v>
       </c>
       <c r="W73">
-        <v>0.2296676933485985</v>
+        <v>0.2297528642743124</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1182108615043849</v>
+        <v>0.1165690439834907</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7453,22 +7453,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2179942751123364</v>
+        <v>0.2198942751123365</v>
       </c>
       <c r="C74">
-        <v>-13744.01901553629</v>
+        <v>-14098.62737231586</v>
       </c>
       <c r="D74">
-        <v>6444.452984463715</v>
+        <v>6374.120627684144</v>
       </c>
       <c r="E74">
-        <v>18336.472</v>
+        <v>18620.748</v>
       </c>
       <c r="F74">
-        <v>20467.872</v>
+        <v>20752.148</v>
       </c>
       <c r="G74">
         <v>279.4</v>
@@ -7489,37 +7489,37 @@
         <v>562.6</v>
       </c>
       <c r="M74">
-        <v>4826.3242176</v>
+        <v>4893.3564984</v>
       </c>
       <c r="N74">
-        <v>-4263.7242176</v>
+        <v>-4330.7564984</v>
       </c>
       <c r="O74">
-        <v>-938.019327872</v>
+        <v>-952.766429648</v>
       </c>
       <c r="P74">
-        <v>-3325.704889728</v>
+        <v>-3377.990068752</v>
       </c>
       <c r="Q74">
-        <v>-3173.304889728</v>
+        <v>-3225.590068752</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1877579029815411</v>
+        <v>0.1930156030919686</v>
       </c>
       <c r="T74">
-        <v>3.278473509966307</v>
+        <v>3.399898454779875</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02564518967636792</v>
+        <v>0.02529388570819849</v>
       </c>
       <c r="W74">
-        <v>0.2297528642743124</v>
+        <v>0.2298357017500068</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1165690439834907</v>
+        <v>0.1149722077645386</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7535,22 +7535,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2198942751123365</v>
+        <v>0.2217942751123365</v>
       </c>
       <c r="C75">
-        <v>-14098.62737231586</v>
+        <v>-14451.71714017773</v>
       </c>
       <c r="D75">
-        <v>6374.120627684144</v>
+        <v>6305.306859822268</v>
       </c>
       <c r="E75">
-        <v>18620.748</v>
+        <v>18905.024</v>
       </c>
       <c r="F75">
-        <v>20752.148</v>
+        <v>21036.424</v>
       </c>
       <c r="G75">
         <v>279.4</v>
@@ -7571,37 +7571,37 @@
         <v>562.6</v>
       </c>
       <c r="M75">
-        <v>4893.3564984</v>
+        <v>4960.3887792</v>
       </c>
       <c r="N75">
-        <v>-4330.7564984</v>
+        <v>-4397.7887792</v>
       </c>
       <c r="O75">
-        <v>-952.766429648</v>
+        <v>-967.513531424</v>
       </c>
       <c r="P75">
-        <v>-3377.990068752</v>
+        <v>-3430.275247776</v>
       </c>
       <c r="Q75">
-        <v>-3225.590068752</v>
+        <v>-3277.875247776</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1930156030919686</v>
+        <v>0.1986777416724289</v>
       </c>
       <c r="T75">
-        <v>3.399898454779875</v>
+        <v>3.530663779963715</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02529388570819849</v>
+        <v>0.02495207644187149</v>
       </c>
       <c r="W75">
-        <v>0.2298357017500068</v>
+        <v>0.2299163003750067</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1149722077645386</v>
+        <v>0.1134185292812341</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7617,22 +7617,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2217942751123365</v>
+        <v>0.2236942751123365</v>
       </c>
       <c r="C76">
-        <v>-14451.71714017773</v>
+        <v>-14803.33697699372</v>
       </c>
       <c r="D76">
-        <v>6305.306859822268</v>
+        <v>6237.963023006286</v>
       </c>
       <c r="E76">
-        <v>18905.024</v>
+        <v>19189.3</v>
       </c>
       <c r="F76">
-        <v>21036.424</v>
+        <v>21320.7</v>
       </c>
       <c r="G76">
         <v>279.4</v>
@@ -7653,37 +7653,37 @@
         <v>562.6</v>
       </c>
       <c r="M76">
-        <v>4960.3887792</v>
+        <v>5027.421060000001</v>
       </c>
       <c r="N76">
-        <v>-4397.7887792</v>
+        <v>-4464.82106</v>
       </c>
       <c r="O76">
-        <v>-967.513531424</v>
+        <v>-982.2606332</v>
       </c>
       <c r="P76">
-        <v>-3430.275247776</v>
+        <v>-3482.5604268</v>
       </c>
       <c r="Q76">
-        <v>-3277.875247776</v>
+        <v>-3330.1604268</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1986777416724289</v>
+        <v>0.204792851339326</v>
       </c>
       <c r="T76">
-        <v>3.530663779963715</v>
+        <v>3.671890331162265</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02495207644187149</v>
+        <v>0.0246193820893132</v>
       </c>
       <c r="W76">
-        <v>0.2299163003750067</v>
+        <v>0.2299947497033399</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1134185292812341</v>
+        <v>0.111906282224151</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7699,22 +7699,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2236942751123365</v>
+        <v>0.2255942751123365</v>
       </c>
       <c r="C77">
-        <v>-14803.33697699372</v>
+        <v>-15153.53348384137</v>
       </c>
       <c r="D77">
-        <v>6237.963023006286</v>
+        <v>6172.042516158632</v>
       </c>
       <c r="E77">
-        <v>19189.3</v>
+        <v>19473.576</v>
       </c>
       <c r="F77">
-        <v>21320.7</v>
+        <v>21604.976</v>
       </c>
       <c r="G77">
         <v>279.4</v>
@@ -7735,37 +7735,37 @@
         <v>562.6</v>
       </c>
       <c r="M77">
-        <v>5027.421060000001</v>
+        <v>5094.453340800001</v>
       </c>
       <c r="N77">
-        <v>-4464.82106</v>
+        <v>-4531.8533408</v>
       </c>
       <c r="O77">
-        <v>-982.2606332</v>
+        <v>-997.0077349760001</v>
       </c>
       <c r="P77">
-        <v>-3482.5604268</v>
+        <v>-3534.845605824</v>
       </c>
       <c r="Q77">
-        <v>-3330.1604268</v>
+        <v>-3382.445605824</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.204792851339326</v>
+        <v>0.2114175534784646</v>
       </c>
       <c r="T77">
-        <v>3.671890331162265</v>
+        <v>3.824885761627359</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0246193820893132</v>
+        <v>0.02429544285129592</v>
       </c>
       <c r="W77">
-        <v>0.2299947497033399</v>
+        <v>0.2300711345756644</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.111906282224151</v>
+        <v>0.1104338311422542</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7781,22 +7781,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2255942751123365</v>
+        <v>0.2274942751123365</v>
       </c>
       <c r="C78">
-        <v>-15153.53348384137</v>
+        <v>-15502.35131254484</v>
       </c>
       <c r="D78">
-        <v>6172.042516158632</v>
+        <v>6107.500687455163</v>
       </c>
       <c r="E78">
-        <v>19473.576</v>
+        <v>19757.852</v>
       </c>
       <c r="F78">
-        <v>21604.976</v>
+        <v>21889.252</v>
       </c>
       <c r="G78">
         <v>279.4</v>
@@ -7817,37 +7817,37 @@
         <v>562.6</v>
       </c>
       <c r="M78">
-        <v>5094.453340800001</v>
+        <v>5161.485621600001</v>
       </c>
       <c r="N78">
-        <v>-4531.8533408</v>
+        <v>-4598.8856216</v>
       </c>
       <c r="O78">
-        <v>-997.0077349760001</v>
+        <v>-1011.754836752</v>
       </c>
       <c r="P78">
-        <v>-3534.845605824</v>
+        <v>-3587.130784848</v>
       </c>
       <c r="Q78">
-        <v>-3382.445605824</v>
+        <v>-3434.730784848</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2114175534784646</v>
+        <v>0.2186183166731805</v>
       </c>
       <c r="T78">
-        <v>3.824885761627359</v>
+        <v>3.991185142567679</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02429544285129592</v>
+        <v>0.02397991761946091</v>
       </c>
       <c r="W78">
-        <v>0.2300711345756644</v>
+        <v>0.2301455354253311</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1104338311422542</v>
+        <v>0.1089996255430042</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7863,22 +7863,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2274942751123365</v>
+        <v>0.2293942751123365</v>
       </c>
       <c r="C79">
-        <v>-15502.35131254484</v>
+        <v>-15849.83326653804</v>
       </c>
       <c r="D79">
-        <v>6107.500687455163</v>
+        <v>6044.294733461965</v>
       </c>
       <c r="E79">
-        <v>19757.852</v>
+        <v>20042.128</v>
       </c>
       <c r="F79">
-        <v>21889.252</v>
+        <v>22173.528</v>
       </c>
       <c r="G79">
         <v>279.4</v>
@@ -7899,37 +7899,37 @@
         <v>562.6</v>
       </c>
       <c r="M79">
-        <v>5161.485621600001</v>
+        <v>5228.517902400001</v>
       </c>
       <c r="N79">
-        <v>-4598.8856216</v>
+        <v>-4665.9179024</v>
       </c>
       <c r="O79">
-        <v>-1011.754836752</v>
+        <v>-1026.501938528</v>
       </c>
       <c r="P79">
-        <v>-3587.130784848</v>
+        <v>-3639.415963872</v>
       </c>
       <c r="Q79">
-        <v>-3434.730784848</v>
+        <v>-3487.015963872</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2186183166731805</v>
+        <v>0.2264736947037796</v>
       </c>
       <c r="T79">
-        <v>3.991185142567679</v>
+        <v>4.172602649048028</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02397991761946091</v>
+        <v>0.02367248277818577</v>
       </c>
       <c r="W79">
-        <v>0.2301455354253311</v>
+        <v>0.2302180285609038</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1089996255430042</v>
+        <v>0.107602194446299</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7945,22 +7945,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2293942751123365</v>
+        <v>0.2312942751123365</v>
       </c>
       <c r="C80">
-        <v>-15849.83326653804</v>
+        <v>-16196.02039552907</v>
       </c>
       <c r="D80">
-        <v>6044.294733461965</v>
+        <v>5982.383604470934</v>
       </c>
       <c r="E80">
-        <v>20042.128</v>
+        <v>20326.404</v>
       </c>
       <c r="F80">
-        <v>22173.528</v>
+        <v>22457.804</v>
       </c>
       <c r="G80">
         <v>279.4</v>
@@ -7981,37 +7981,37 @@
         <v>562.6</v>
       </c>
       <c r="M80">
-        <v>5228.517902400001</v>
+        <v>5295.550183200001</v>
       </c>
       <c r="N80">
-        <v>-4665.9179024</v>
+        <v>-4732.950183200001</v>
       </c>
       <c r="O80">
-        <v>-1026.501938528</v>
+        <v>-1041.249040304</v>
       </c>
       <c r="P80">
-        <v>-3639.415963872</v>
+        <v>-3691.701142896</v>
       </c>
       <c r="Q80">
-        <v>-3487.015963872</v>
+        <v>-3539.301142896</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2264736947037796</v>
+        <v>0.2350772039753882</v>
       </c>
       <c r="T80">
-        <v>4.172602649048028</v>
+        <v>4.371298013288412</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02367248277818577</v>
+        <v>0.02337283109744924</v>
       </c>
       <c r="W80">
-        <v>0.2302180285609038</v>
+        <v>0.2302886864272215</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.107602194446299</v>
+        <v>0.1062401413520421</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8027,22 +8027,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2312942751123365</v>
+        <v>0.2331942751123365</v>
       </c>
       <c r="C81">
-        <v>-16196.02039552907</v>
+        <v>-16540.9520844058</v>
       </c>
       <c r="D81">
-        <v>5982.383604470934</v>
+        <v>5921.727915594201</v>
       </c>
       <c r="E81">
-        <v>20326.404</v>
+        <v>20610.68</v>
       </c>
       <c r="F81">
-        <v>22457.804</v>
+        <v>22742.08</v>
       </c>
       <c r="G81">
         <v>279.4</v>
@@ -8063,37 +8063,37 @@
         <v>562.6</v>
       </c>
       <c r="M81">
-        <v>5295.550183200001</v>
+        <v>5362.582464000001</v>
       </c>
       <c r="N81">
-        <v>-4732.950183200001</v>
+        <v>-4799.982464000001</v>
       </c>
       <c r="O81">
-        <v>-1041.249040304</v>
+        <v>-1055.99614208</v>
       </c>
       <c r="P81">
-        <v>-3691.701142896</v>
+        <v>-3743.986321920001</v>
       </c>
       <c r="Q81">
-        <v>-3539.301142896</v>
+        <v>-3591.586321920001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2350772039753882</v>
+        <v>0.2445410641741576</v>
       </c>
       <c r="T81">
-        <v>4.371298013288412</v>
+        <v>4.589862913952832</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02337283109744924</v>
+        <v>0.02308067070873113</v>
       </c>
       <c r="W81">
-        <v>0.2302886864272215</v>
+        <v>0.2303575778468812</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1062401413520421</v>
+        <v>0.1049121395851416</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8109,22 +8109,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2331942751123365</v>
+        <v>0.2350942751123365</v>
       </c>
       <c r="C82">
-        <v>-16540.9520844058</v>
+        <v>-16884.66613678722</v>
       </c>
       <c r="D82">
-        <v>5921.727915594201</v>
+        <v>5862.289863212784</v>
       </c>
       <c r="E82">
-        <v>20610.68</v>
+        <v>20894.956</v>
       </c>
       <c r="F82">
-        <v>22742.08</v>
+        <v>23026.356</v>
       </c>
       <c r="G82">
         <v>279.4</v>
@@ -8145,37 +8145,37 @@
         <v>562.6</v>
       </c>
       <c r="M82">
-        <v>5362.582464000001</v>
+        <v>5429.614744800001</v>
       </c>
       <c r="N82">
-        <v>-4799.982464000001</v>
+        <v>-4867.014744800001</v>
       </c>
       <c r="O82">
-        <v>-1055.99614208</v>
+        <v>-1070.743243856</v>
       </c>
       <c r="P82">
-        <v>-3743.986321920001</v>
+        <v>-3796.271500944001</v>
       </c>
       <c r="Q82">
-        <v>-3591.586321920001</v>
+        <v>-3643.871500944001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2445410641741576</v>
+        <v>0.2550011201833238</v>
       </c>
       <c r="T82">
-        <v>4.589862913952832</v>
+        <v>4.831434646266139</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02308067070873113</v>
+        <v>0.02279572415677148</v>
       </c>
       <c r="W82">
-        <v>0.2303575778468812</v>
+        <v>0.2304247682438333</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1049121395851416</v>
+        <v>0.103616927985325</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8191,22 +8191,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2350942751123365</v>
+        <v>0.2369942751123364</v>
       </c>
       <c r="C83">
-        <v>-16884.66613678722</v>
+        <v>-17227.19885359299</v>
       </c>
       <c r="D83">
-        <v>5862.289863212784</v>
+        <v>5804.033146407012</v>
       </c>
       <c r="E83">
-        <v>20894.956</v>
+        <v>21179.232</v>
       </c>
       <c r="F83">
-        <v>23026.356</v>
+        <v>23310.63200000001</v>
       </c>
       <c r="G83">
         <v>279.4</v>
@@ -8227,37 +8227,37 @@
         <v>562.6</v>
       </c>
       <c r="M83">
-        <v>5429.614744800001</v>
+        <v>5496.647025600001</v>
       </c>
       <c r="N83">
-        <v>-4867.014744800001</v>
+        <v>-4934.047025600001</v>
       </c>
       <c r="O83">
-        <v>-1070.743243856</v>
+        <v>-1085.490345632</v>
       </c>
       <c r="P83">
-        <v>-3796.271500944001</v>
+        <v>-3848.556679968001</v>
       </c>
       <c r="Q83">
-        <v>-3643.871500944001</v>
+        <v>-3696.156679968001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2550011201833238</v>
+        <v>0.2666234046379528</v>
       </c>
       <c r="T83">
-        <v>4.831434646266139</v>
+        <v>5.099847682169813</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02279572415677148</v>
+        <v>0.02251772752071329</v>
       </c>
       <c r="W83">
-        <v>0.2304247682438333</v>
+        <v>0.2304903198506158</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.103616927985325</v>
+        <v>0.1023533069123332</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8273,22 +8273,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2369942751123364</v>
+        <v>0.2388942751123365</v>
       </c>
       <c r="C84">
-        <v>-17227.19885359299</v>
+        <v>-17568.58510697444</v>
       </c>
       <c r="D84">
-        <v>5804.033146407012</v>
+        <v>5746.922893025561</v>
       </c>
       <c r="E84">
-        <v>21179.232</v>
+        <v>21463.508</v>
       </c>
       <c r="F84">
-        <v>23310.63200000001</v>
+        <v>23594.908</v>
       </c>
       <c r="G84">
         <v>279.4</v>
@@ -8309,37 +8309,37 @@
         <v>562.6</v>
       </c>
       <c r="M84">
-        <v>5496.647025600001</v>
+        <v>5563.679306400001</v>
       </c>
       <c r="N84">
-        <v>-4934.047025600001</v>
+        <v>-5001.079306400001</v>
       </c>
       <c r="O84">
-        <v>-1085.490345632</v>
+        <v>-1100.237447408</v>
       </c>
       <c r="P84">
-        <v>-3848.556679968001</v>
+        <v>-3900.841858992001</v>
       </c>
       <c r="Q84">
-        <v>-3696.156679968001</v>
+        <v>-3748.441858992001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2666234046379528</v>
+        <v>0.2796130166754796</v>
       </c>
       <c r="T84">
-        <v>5.099847682169813</v>
+        <v>5.39983872229745</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02251772752071329</v>
+        <v>0.02224642959877699</v>
       </c>
       <c r="W84">
-        <v>0.2304903198506158</v>
+        <v>0.2305542919006084</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1023533069123332</v>
+        <v>0.1011201345398954</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8355,22 +8355,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2388942751123365</v>
+        <v>0.2407942751123365</v>
       </c>
       <c r="C85">
-        <v>-17568.58510697444</v>
+        <v>-17908.85840992325</v>
       </c>
       <c r="D85">
-        <v>5746.922893025561</v>
+        <v>5690.925590076753</v>
       </c>
       <c r="E85">
-        <v>21463.508</v>
+        <v>21747.784</v>
       </c>
       <c r="F85">
-        <v>23594.908</v>
+        <v>23879.184</v>
       </c>
       <c r="G85">
         <v>279.4</v>
@@ -8391,37 +8391,37 @@
         <v>562.6</v>
       </c>
       <c r="M85">
-        <v>5563.679306400001</v>
+        <v>5630.711587200001</v>
       </c>
       <c r="N85">
-        <v>-5001.079306400001</v>
+        <v>-5068.111587200001</v>
       </c>
       <c r="O85">
-        <v>-1100.237447408</v>
+        <v>-1114.984549184</v>
       </c>
       <c r="P85">
-        <v>-3900.841858992001</v>
+        <v>-3953.127038016001</v>
       </c>
       <c r="Q85">
-        <v>-3748.441858992001</v>
+        <v>-3800.727038016001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2796130166754796</v>
+        <v>0.2942263302176971</v>
       </c>
       <c r="T85">
-        <v>5.39983872229745</v>
+        <v>5.737328642441042</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02224642959877699</v>
+        <v>0.0219815911511725</v>
       </c>
       <c r="W85">
-        <v>0.2305542919006084</v>
+        <v>0.2306167408065535</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1011201345398954</v>
+        <v>0.09991632341442047</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8437,22 +8437,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2407942751123365</v>
+        <v>0.2426942751123365</v>
       </c>
       <c r="C86">
-        <v>-17908.85840992325</v>
+        <v>-18248.05098184987</v>
       </c>
       <c r="D86">
-        <v>5690.925590076753</v>
+        <v>5636.009018150135</v>
       </c>
       <c r="E86">
-        <v>21747.784</v>
+        <v>22032.06</v>
       </c>
       <c r="F86">
-        <v>23879.184</v>
+        <v>24163.46</v>
       </c>
       <c r="G86">
         <v>279.4</v>
@@ -8473,37 +8473,37 @@
         <v>562.6</v>
       </c>
       <c r="M86">
-        <v>5630.7115872</v>
+        <v>5697.743868</v>
       </c>
       <c r="N86">
-        <v>-5068.1115872</v>
+        <v>-5135.143868</v>
       </c>
       <c r="O86">
-        <v>-1114.984549184</v>
+        <v>-1129.73165096</v>
       </c>
       <c r="P86">
-        <v>-3953.127038016</v>
+        <v>-4005.41221704</v>
       </c>
       <c r="Q86">
-        <v>-3800.727038016</v>
+        <v>-3853.01221704</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2942263302176969</v>
+        <v>0.3107880855655434</v>
       </c>
       <c r="T86">
-        <v>5.737328642441038</v>
+        <v>6.119817218603774</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0219815911511725</v>
+        <v>0.02172298419645282</v>
       </c>
       <c r="W86">
-        <v>0.2306167408065535</v>
+        <v>0.2306777203264764</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09991632341442047</v>
+        <v>0.09874083725660376</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8519,22 +8519,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2426942751123365</v>
+        <v>0.2445942751123365</v>
       </c>
       <c r="C87">
-        <v>-18248.05098184987</v>
+        <v>-18586.19381040131</v>
       </c>
       <c r="D87">
-        <v>5636.009018150135</v>
+        <v>5582.142189598689</v>
       </c>
       <c r="E87">
-        <v>22032.06</v>
+        <v>22316.336</v>
       </c>
       <c r="F87">
-        <v>24163.46</v>
+        <v>24447.736</v>
       </c>
       <c r="G87">
         <v>279.4</v>
@@ -8555,37 +8555,37 @@
         <v>562.6</v>
       </c>
       <c r="M87">
-        <v>5697.743868</v>
+        <v>5764.776148800001</v>
       </c>
       <c r="N87">
-        <v>-5135.143868</v>
+        <v>-5202.1761488</v>
       </c>
       <c r="O87">
-        <v>-1129.73165096</v>
+        <v>-1144.478752736</v>
       </c>
       <c r="P87">
-        <v>-4005.41221704</v>
+        <v>-4057.697396064</v>
       </c>
       <c r="Q87">
-        <v>-3853.01221704</v>
+        <v>-3905.297396064</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3107880855655434</v>
+        <v>0.3297158059630822</v>
       </c>
       <c r="T87">
-        <v>6.119817218603774</v>
+        <v>6.556947019932616</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02172298419645282</v>
+        <v>0.02147039135695919</v>
       </c>
       <c r="W87">
-        <v>0.2306777203264764</v>
+        <v>0.230737281718029</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.09874083725660376</v>
+        <v>0.09759268798617815</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8601,22 +8601,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2445942751123365</v>
+        <v>0.2464942751123365</v>
       </c>
       <c r="C88">
-        <v>-18586.19381040131</v>
+        <v>-18923.31670976753</v>
       </c>
       <c r="D88">
-        <v>5582.142189598689</v>
+        <v>5529.295290232473</v>
       </c>
       <c r="E88">
-        <v>22316.336</v>
+        <v>22600.612</v>
       </c>
       <c r="F88">
-        <v>24447.736</v>
+        <v>24732.012</v>
       </c>
       <c r="G88">
         <v>279.4</v>
@@ -8637,37 +8637,37 @@
         <v>562.6</v>
       </c>
       <c r="M88">
-        <v>5764.776148800001</v>
+        <v>5831.808429600001</v>
       </c>
       <c r="N88">
-        <v>-5202.1761488</v>
+        <v>-5269.2084296</v>
       </c>
       <c r="O88">
-        <v>-1144.478752736</v>
+        <v>-1159.225854512</v>
       </c>
       <c r="P88">
-        <v>-4057.697396064</v>
+        <v>-4109.982575088</v>
       </c>
       <c r="Q88">
-        <v>-3905.297396064</v>
+        <v>-3957.582575088</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3297158059630822</v>
+        <v>0.3515554833448577</v>
       </c>
       <c r="T88">
-        <v>6.556947019932616</v>
+        <v>7.061327559927431</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02147039135695919</v>
+        <v>0.02122360524940793</v>
       </c>
       <c r="W88">
-        <v>0.230737281718029</v>
+        <v>0.2307954738821896</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8675,7 +8675,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09759268798617815</v>
+        <v>0.09647093295185427</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8683,22 +8683,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2464942751123365</v>
+        <v>0.2483942751123365</v>
       </c>
       <c r="C89">
-        <v>-18923.31670976753</v>
+        <v>-19259.44837570684</v>
       </c>
       <c r="D89">
-        <v>5529.295290232473</v>
+        <v>5477.439624293164</v>
       </c>
       <c r="E89">
-        <v>22600.612</v>
+        <v>22884.888</v>
       </c>
       <c r="F89">
-        <v>24732.012</v>
+        <v>25016.288</v>
       </c>
       <c r="G89">
         <v>279.4</v>
@@ -8719,37 +8719,37 @@
         <v>562.6</v>
       </c>
       <c r="M89">
-        <v>5831.808429600001</v>
+        <v>5898.840710400001</v>
       </c>
       <c r="N89">
-        <v>-5269.2084296</v>
+        <v>-5336.2407104</v>
       </c>
       <c r="O89">
-        <v>-1159.225854512</v>
+        <v>-1173.972956288</v>
       </c>
       <c r="P89">
-        <v>-4109.982575088</v>
+        <v>-4162.267754112</v>
       </c>
       <c r="Q89">
-        <v>-3957.582575088</v>
+        <v>-4009.867754112</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3515554833448577</v>
+        <v>0.3770351069569292</v>
       </c>
       <c r="T89">
-        <v>7.061327559927431</v>
+        <v>7.649771523254717</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02122360524940793</v>
+        <v>0.0209824279170283</v>
       </c>
       <c r="W89">
-        <v>0.2307954738821896</v>
+        <v>0.2308523434971647</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.09647093295185427</v>
+        <v>0.09537467235012864</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8765,22 +8765,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2483942751123365</v>
+        <v>0.2502942751123365</v>
       </c>
       <c r="C90">
-        <v>-19259.44837570684</v>
+        <v>-19594.61643750387</v>
       </c>
       <c r="D90">
-        <v>5477.439624293164</v>
+        <v>5426.54756249613</v>
       </c>
       <c r="E90">
-        <v>22884.888</v>
+        <v>23169.164</v>
       </c>
       <c r="F90">
-        <v>25016.288</v>
+        <v>25300.564</v>
       </c>
       <c r="G90">
         <v>279.4</v>
@@ -8801,37 +8801,37 @@
         <v>562.6</v>
       </c>
       <c r="M90">
-        <v>5898.840710400001</v>
+        <v>5965.872991200001</v>
       </c>
       <c r="N90">
-        <v>-5336.2407104</v>
+        <v>-5403.2729912</v>
       </c>
       <c r="O90">
-        <v>-1173.972956288</v>
+        <v>-1188.720058064</v>
       </c>
       <c r="P90">
-        <v>-4162.267754112</v>
+        <v>-4214.552933136</v>
       </c>
       <c r="Q90">
-        <v>-4009.867754112</v>
+        <v>-4062.152933136</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3770351069569292</v>
+        <v>0.4071473894075592</v>
       </c>
       <c r="T90">
-        <v>7.649771523254717</v>
+        <v>8.345205298096056</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0209824279170283</v>
+        <v>0.02074667029998303</v>
       </c>
       <c r="W90">
-        <v>0.2308523434971647</v>
+        <v>0.230907935143264</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.09537467235012864</v>
+        <v>0.09430304681810475</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8847,22 +8847,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2502942751123365</v>
+        <v>0.2521942751123365</v>
       </c>
       <c r="C91">
-        <v>-19594.61643750387</v>
+        <v>-19928.84750705768</v>
       </c>
       <c r="D91">
-        <v>5426.54756249613</v>
+        <v>5376.59249294233</v>
       </c>
       <c r="E91">
-        <v>23169.164</v>
+        <v>23453.44</v>
       </c>
       <c r="F91">
-        <v>25300.564</v>
+        <v>25584.84</v>
       </c>
       <c r="G91">
         <v>279.4</v>
@@ -8883,37 +8883,37 @@
         <v>562.6</v>
       </c>
       <c r="M91">
-        <v>5965.872991200001</v>
+        <v>6032.905272000001</v>
       </c>
       <c r="N91">
-        <v>-5403.2729912</v>
+        <v>-5470.305272000001</v>
       </c>
       <c r="O91">
-        <v>-1188.720058064</v>
+        <v>-1203.46715984</v>
       </c>
       <c r="P91">
-        <v>-4214.552933136</v>
+        <v>-4266.83811216</v>
       </c>
       <c r="Q91">
-        <v>-4062.152933136</v>
+        <v>-4114.438112160001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4071473894075592</v>
+        <v>0.4432821283483152</v>
       </c>
       <c r="T91">
-        <v>8.345205298096056</v>
+        <v>9.179725827905663</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02074667029998303</v>
+        <v>0.02051615174109433</v>
       </c>
       <c r="W91">
-        <v>0.230907935143264</v>
+        <v>0.23096229141945</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.09430304681810475</v>
+        <v>0.09325523518679246</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8929,22 +8929,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2521942751123365</v>
+        <v>0.2540942751123365</v>
       </c>
       <c r="C92">
-        <v>-19928.84750705768</v>
+        <v>-20262.16722528316</v>
       </c>
       <c r="D92">
-        <v>5376.59249294233</v>
+        <v>5327.548774716847</v>
       </c>
       <c r="E92">
-        <v>23453.44</v>
+        <v>23737.716</v>
       </c>
       <c r="F92">
-        <v>25584.84</v>
+        <v>25869.116</v>
       </c>
       <c r="G92">
         <v>279.4</v>
@@ -8965,37 +8965,37 @@
         <v>562.6</v>
       </c>
       <c r="M92">
-        <v>6032.905272000001</v>
+        <v>6099.937552800001</v>
       </c>
       <c r="N92">
-        <v>-5470.305272000001</v>
+        <v>-5537.337552800001</v>
       </c>
       <c r="O92">
-        <v>-1203.46715984</v>
+        <v>-1218.214261616</v>
       </c>
       <c r="P92">
-        <v>-4266.83811216</v>
+        <v>-4319.123291184001</v>
       </c>
       <c r="Q92">
-        <v>-4114.438112160001</v>
+        <v>-4166.723291184001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4432821283483152</v>
+        <v>0.4874468092759058</v>
       </c>
       <c r="T92">
-        <v>9.179725827905663</v>
+        <v>10.19969536433963</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02051615174109433</v>
+        <v>0.02029069952415923</v>
       </c>
       <c r="W92">
-        <v>0.23096229141945</v>
+        <v>0.2310154530522033</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.09325523518679246</v>
+        <v>0.09223045238254202</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9011,22 +9011,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2540942751123365</v>
+        <v>0.2559942751123365</v>
       </c>
       <c r="C93">
-        <v>-20262.16722528316</v>
+        <v>-20594.600305996</v>
       </c>
       <c r="D93">
-        <v>5327.548774716847</v>
+        <v>5279.391694004005</v>
       </c>
       <c r="E93">
-        <v>23737.716</v>
+        <v>24021.992</v>
       </c>
       <c r="F93">
-        <v>25869.116</v>
+        <v>26153.392</v>
       </c>
       <c r="G93">
         <v>279.4</v>
@@ -9047,37 +9047,37 @@
         <v>562.6</v>
       </c>
       <c r="M93">
-        <v>6099.937552800001</v>
+        <v>6166.969833600001</v>
       </c>
       <c r="N93">
-        <v>-5537.337552800001</v>
+        <v>-5604.369833600001</v>
       </c>
       <c r="O93">
-        <v>-1218.214261616</v>
+        <v>-1232.961363392</v>
       </c>
       <c r="P93">
-        <v>-4319.123291184001</v>
+        <v>-4371.408470208001</v>
       </c>
       <c r="Q93">
-        <v>-4166.723291184001</v>
+        <v>-4219.008470208001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4874468092759058</v>
+        <v>0.5426526604353942</v>
       </c>
       <c r="T93">
-        <v>10.19969536433963</v>
+        <v>11.47465728488208</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02029069952415923</v>
+        <v>0.02007014844237489</v>
       </c>
       <c r="W93">
-        <v>0.2310154530522033</v>
+        <v>0.231067458997288</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.09223045238254202</v>
+        <v>0.09122794746534046</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9093,22 +9093,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2559942751123365</v>
+        <v>0.2578942751123365</v>
       </c>
       <c r="C94">
-        <v>-20594.600305996</v>
+        <v>-20926.17057743871</v>
       </c>
       <c r="D94">
-        <v>5279.391694004005</v>
+        <v>5232.097422561296</v>
       </c>
       <c r="E94">
-        <v>24021.992</v>
+        <v>24306.268</v>
       </c>
       <c r="F94">
-        <v>26153.392</v>
+        <v>26437.66800000001</v>
       </c>
       <c r="G94">
         <v>279.4</v>
@@ -9129,37 +9129,37 @@
         <v>562.6</v>
       </c>
       <c r="M94">
-        <v>6166.969833600001</v>
+        <v>6234.002114400001</v>
       </c>
       <c r="N94">
-        <v>-5604.369833600001</v>
+        <v>-5671.402114400001</v>
       </c>
       <c r="O94">
-        <v>-1232.961363392</v>
+        <v>-1247.708465168</v>
       </c>
       <c r="P94">
-        <v>-4371.408470208001</v>
+        <v>-4423.693649232</v>
       </c>
       <c r="Q94">
-        <v>-4219.008470208001</v>
+        <v>-4271.293649232</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5426526604353942</v>
+        <v>0.6136316119261648</v>
       </c>
       <c r="T94">
-        <v>11.47465728488208</v>
+        <v>13.11389403986524</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02007014844237489</v>
+        <v>0.01985434039460742</v>
       </c>
       <c r="W94">
-        <v>0.231067458997288</v>
+        <v>0.2311183465349516</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.09122794746534046</v>
+        <v>0.09024700179367018</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9175,22 +9175,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2578942751123365</v>
+        <v>0.2597942751123365</v>
       </c>
       <c r="C95">
-        <v>-20926.17057743871</v>
+        <v>-21256.90102159451</v>
       </c>
       <c r="D95">
-        <v>5232.097422561296</v>
+        <v>5185.642978405498</v>
       </c>
       <c r="E95">
-        <v>24306.268</v>
+        <v>24590.544</v>
       </c>
       <c r="F95">
-        <v>26437.66800000001</v>
+        <v>26721.944</v>
       </c>
       <c r="G95">
         <v>279.4</v>
@@ -9211,37 +9211,37 @@
         <v>562.6</v>
       </c>
       <c r="M95">
-        <v>6234.002114400001</v>
+        <v>6301.034395200001</v>
       </c>
       <c r="N95">
-        <v>-5671.402114400001</v>
+        <v>-5738.434395200001</v>
       </c>
       <c r="O95">
-        <v>-1247.708465168</v>
+        <v>-1262.455566944</v>
       </c>
       <c r="P95">
-        <v>-4423.693649232</v>
+        <v>-4475.978828256</v>
       </c>
       <c r="Q95">
-        <v>-4271.293649232</v>
+        <v>-4323.578828256001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6136316119261648</v>
+        <v>0.7082702139138591</v>
       </c>
       <c r="T95">
-        <v>13.11389403986524</v>
+        <v>15.29954304650945</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01985434039460742</v>
+        <v>0.01964312400743074</v>
       </c>
       <c r="W95">
-        <v>0.2311183465349516</v>
+        <v>0.2311681513590478</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.09024700179367018</v>
+        <v>0.08928692730650345</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9257,22 +9257,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2597942751123365</v>
+        <v>0.2616942751123364</v>
       </c>
       <c r="C96">
-        <v>-21256.90102159451</v>
+        <v>-21586.81381142529</v>
       </c>
       <c r="D96">
-        <v>5185.642978405498</v>
+        <v>5140.006188574719</v>
       </c>
       <c r="E96">
-        <v>24590.544</v>
+        <v>24874.82</v>
       </c>
       <c r="F96">
-        <v>26721.944</v>
+        <v>27006.22</v>
       </c>
       <c r="G96">
         <v>279.4</v>
@@ -9293,37 +9293,37 @@
         <v>562.6</v>
       </c>
       <c r="M96">
-        <v>6301.034395200001</v>
+        <v>6368.066676000001</v>
       </c>
       <c r="N96">
-        <v>-5738.434395200001</v>
+        <v>-5805.466676000001</v>
       </c>
       <c r="O96">
-        <v>-1262.455566944</v>
+        <v>-1277.20266872</v>
       </c>
       <c r="P96">
-        <v>-4475.978828256</v>
+        <v>-4528.26400728</v>
       </c>
       <c r="Q96">
-        <v>-4323.578828256001</v>
+        <v>-4375.864007280001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7082702139138591</v>
+        <v>0.8407642566966311</v>
       </c>
       <c r="T96">
-        <v>15.29954304650945</v>
+        <v>18.35945165581135</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01964312400743074</v>
+        <v>0.01943635428103673</v>
       </c>
       <c r="W96">
-        <v>0.2311681513590478</v>
+        <v>0.2312169076605315</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.08928692730650345</v>
+        <v>0.0883470649138034</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9339,22 +9339,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2616942751123364</v>
+        <v>0.2635942751123365</v>
       </c>
       <c r="C97">
-        <v>-21586.81381142529</v>
+        <v>-21915.93034616044</v>
       </c>
       <c r="D97">
-        <v>5140.006188574719</v>
+        <v>5095.165653839565</v>
       </c>
       <c r="E97">
-        <v>24874.82</v>
+        <v>25159.096</v>
       </c>
       <c r="F97">
-        <v>27006.22</v>
+        <v>27290.496</v>
       </c>
       <c r="G97">
         <v>279.4</v>
@@ -9375,37 +9375,37 @@
         <v>562.6</v>
       </c>
       <c r="M97">
-        <v>6368.066676000001</v>
+        <v>6435.098956800001</v>
       </c>
       <c r="N97">
-        <v>-5805.466676000001</v>
+        <v>-5872.498956800001</v>
       </c>
       <c r="O97">
-        <v>-1277.20266872</v>
+        <v>-1291.949770496</v>
       </c>
       <c r="P97">
-        <v>-4528.26400728</v>
+        <v>-4580.549186304001</v>
       </c>
       <c r="Q97">
-        <v>-4375.864007280001</v>
+        <v>-4428.149186304001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8407642566966311</v>
+        <v>1.03950532087079</v>
       </c>
       <c r="T97">
-        <v>18.35945165581135</v>
+        <v>22.9493145697642</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01943635428103673</v>
+        <v>0.01923389225727594</v>
       </c>
       <c r="W97">
-        <v>0.2312169076605315</v>
+        <v>0.2312646482057344</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.0883470649138034</v>
+        <v>0.08742678298761797</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9421,22 +9421,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2635942751123365</v>
+        <v>0.2654942751123365</v>
       </c>
       <c r="C98">
-        <v>-21915.93034616044</v>
+        <v>-22244.27128475451</v>
       </c>
       <c r="D98">
-        <v>5095.165653839567</v>
+        <v>5051.10071524549</v>
       </c>
       <c r="E98">
-        <v>25159.096</v>
+        <v>25443.372</v>
       </c>
       <c r="F98">
-        <v>27290.496</v>
+        <v>27574.772</v>
       </c>
       <c r="G98">
         <v>279.4</v>
@@ -9457,37 +9457,37 @@
         <v>562.6</v>
       </c>
       <c r="M98">
-        <v>6435.098956800001</v>
+        <v>6502.131237600001</v>
       </c>
       <c r="N98">
-        <v>-5872.498956800001</v>
+        <v>-5939.5312376</v>
       </c>
       <c r="O98">
-        <v>-1291.949770496</v>
+        <v>-1306.696872272</v>
       </c>
       <c r="P98">
-        <v>-4580.549186304001</v>
+        <v>-4632.834365328</v>
       </c>
       <c r="Q98">
-        <v>-4428.149186304001</v>
+        <v>-4480.434365328</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.039505320870787</v>
+        <v>1.370740427827716</v>
       </c>
       <c r="T98">
-        <v>22.94931456976413</v>
+        <v>30.59908609301885</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01923389225727594</v>
+        <v>0.01903560470823186</v>
       </c>
       <c r="W98">
-        <v>0.2312646482057344</v>
+        <v>0.2313114044097989</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08742678298761797</v>
+        <v>0.0865254759465085</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9503,22 +9503,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2654942751123365</v>
+        <v>0.2673942751123365</v>
       </c>
       <c r="C99">
-        <v>-22244.27128475451</v>
+        <v>-22571.85657762366</v>
       </c>
       <c r="D99">
-        <v>5051.10071524549</v>
+        <v>5007.791422376344</v>
       </c>
       <c r="E99">
-        <v>25443.372</v>
+        <v>25727.648</v>
       </c>
       <c r="F99">
-        <v>27574.772</v>
+        <v>27859.048</v>
       </c>
       <c r="G99">
         <v>279.4</v>
@@ -9539,37 +9539,37 @@
         <v>562.6</v>
       </c>
       <c r="M99">
-        <v>6502.131237600001</v>
+        <v>6569.163518400001</v>
       </c>
       <c r="N99">
-        <v>-5939.5312376</v>
+        <v>-6006.5635184</v>
       </c>
       <c r="O99">
-        <v>-1306.696872272</v>
+        <v>-1321.443974048</v>
       </c>
       <c r="P99">
-        <v>-4632.834365328</v>
+        <v>-4685.119544352</v>
       </c>
       <c r="Q99">
-        <v>-4480.434365328</v>
+        <v>-4532.719544352</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.370740427827716</v>
+        <v>2.033210641741574</v>
       </c>
       <c r="T99">
-        <v>30.59908609301885</v>
+        <v>45.89862913952827</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01903560470823186</v>
+        <v>0.01884136384386214</v>
       </c>
       <c r="W99">
-        <v>0.2313114044097989</v>
+        <v>0.2313572064056173</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.0865254759465085</v>
+        <v>0.08564256292664618</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9585,22 +9585,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2673942751123365</v>
+        <v>0.2692942751123364</v>
       </c>
       <c r="C100">
-        <v>-22571.85657762366</v>
+        <v>-22898.70549676323</v>
       </c>
       <c r="D100">
-        <v>5007.791422376344</v>
+        <v>4965.21850323677</v>
       </c>
       <c r="E100">
-        <v>25727.648</v>
+        <v>26011.924</v>
       </c>
       <c r="F100">
-        <v>27859.048</v>
+        <v>28143.324</v>
       </c>
       <c r="G100">
         <v>279.4</v>
@@ -9621,37 +9621,37 @@
         <v>562.6</v>
       </c>
       <c r="M100">
-        <v>6569.163518400001</v>
+        <v>6636.195799200001</v>
       </c>
       <c r="N100">
-        <v>-6006.5635184</v>
+        <v>-6073.5957992</v>
       </c>
       <c r="O100">
-        <v>-1321.443974048</v>
+        <v>-1336.191075824</v>
       </c>
       <c r="P100">
-        <v>-4685.119544352</v>
+        <v>-4737.404723376</v>
       </c>
       <c r="Q100">
-        <v>-4532.719544352</v>
+        <v>-4585.004723376001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.033210641741574</v>
+        <v>4.020621283483147</v>
       </c>
       <c r="T100">
-        <v>45.89862913952827</v>
+        <v>91.79725827905654</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01884136384386214</v>
+        <v>0.01865104703735848</v>
       </c>
       <c r="W100">
-        <v>0.2313572064056173</v>
+        <v>0.2314020831085909</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9659,91 +9659,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.08564256292664618</v>
+        <v>0.08477748653344774</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2692942751123364</v>
-      </c>
-      <c r="C101">
-        <v>-22898.70549676323</v>
-      </c>
-      <c r="D101">
-        <v>4965.21850323677</v>
-      </c>
-      <c r="E101">
-        <v>26011.924</v>
-      </c>
-      <c r="F101">
-        <v>28143.324</v>
-      </c>
-      <c r="G101">
-        <v>279.4</v>
-      </c>
-      <c r="H101">
-        <v>26296.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>715</v>
-      </c>
-      <c r="K101">
-        <v>152.4</v>
-      </c>
-      <c r="L101">
-        <v>562.6</v>
-      </c>
-      <c r="M101">
-        <v>6636.195799200001</v>
-      </c>
-      <c r="N101">
-        <v>-6073.5957992</v>
-      </c>
-      <c r="O101">
-        <v>-1336.191075824</v>
-      </c>
-      <c r="P101">
-        <v>-4737.404723376</v>
-      </c>
-      <c r="Q101">
-        <v>-4585.004723376001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.020621283483147</v>
-      </c>
-      <c r="T101">
-        <v>91.79725827905654</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01865104703735848</v>
-      </c>
-      <c r="W101">
-        <v>0.2314020831085909</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.08477748653344774</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
